--- a/Часы смен/c 05_08/4_МЯЭД_часы_смен_с_05_08_2026_норматив_ВС.xlsx
+++ b/Часы смен/c 05_08/4_МЯЭД_часы_смен_с_05_08_2026_норматив_ВС.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="1412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1411" uniqueCount="1411">
   <si>
     <t/>
   </si>
@@ -59,7 +59,7 @@
         <rFont val="Arial"/>
       </rPr>
       <t xml:space="preserve">
-с 17 июля 2026 года</t>
+на 16 августа 2026 года</t>
     </r>
   </si>
   <si>
@@ -225,7 +225,7 @@
     <t>_______________подпись</t>
   </si>
   <si>
-    <t/>
+    <t xml:space="preserve">изменения по тел. Н/702 от 21.07; Н/830 от 23.07; Н/018 от 03.08; Н/148 от 05.08; Н/246 от 07.08</t>
   </si>
   <si>
     <t>__________________подпись</t>
@@ -659,16 +659,16 @@
     <t>МЯ</t>
   </si>
   <si>
-    <t>8:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6506 - 6507 - 6048 - 6067</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>11:30</t>
+    <t>6:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6814 - 6819 - 6626 - 6639, состав сдают по смене под п.6110</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>9:10</t>
   </si>
   <si>
     <t/>
@@ -762,7 +762,7 @@
     <t>МЯ</t>
   </si>
   <si>
-    <t>9:50</t>
+    <t>9:25</t>
   </si>
   <si>
     <t xml:space="preserve">6024 - 6051 - 6846 - 6849, состав сдают по смене;
@@ -775,7 +775,7 @@
     <t>12:00</t>
   </si>
   <si>
-    <t>12:25
+    <t>12:00
 ПУ</t>
   </si>
   <si>
@@ -968,7 +968,7 @@
     <t>МЯ</t>
   </si>
   <si>
-    <t>10:15</t>
+    <t>9:45</t>
   </si>
   <si>
     <t>8:00</t>
@@ -1013,23 +1013,235 @@
     <t>17:40</t>
   </si>
   <si>
-    <t xml:space="preserve">принимают состав от п.6245, 6578</t>
-  </si>
-  <si>
-    <t>1:30</t>
-  </si>
-  <si>
-    <t>7:50</t>
+    <t xml:space="preserve">6688 - 6673 - 6588</t>
+  </si>
+  <si>
+    <t>2:10</t>
+  </si>
+  <si>
+    <t>8:30</t>
+  </si>
+  <si>
+    <t>4:10</t>
+  </si>
+  <si>
+    <t>ЩЕ</t>
+  </si>
+  <si>
+    <t>2:10
+ЩЕ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6"/>
+        <rFont val="Arial Narrow"/>
+      </rPr>
+      <t>4:10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <rFont val="Arial Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+**</t>
+    </r>
+  </si>
+  <si>
+    <t>62У</t>
+  </si>
+  <si>
+    <t>61У</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>2:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6002 - 6101</t>
+  </si>
+  <si>
+    <t>7:15</t>
+  </si>
+  <si>
+    <t>4:45</t>
   </si>
   <si>
     <t>3:30</t>
   </si>
   <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>6:00</t>
+  </si>
+  <si>
+    <t>Д62</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>6:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6454 - 6459 - 6834 - 6839</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>9:55</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н62</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>3:40</t>
+  </si>
+  <si>
+    <t>5:10</t>
+  </si>
+  <si>
+    <t>5:10</t>
+  </si>
+  <si>
+    <t>МН</t>
+  </si>
+  <si>
+    <t>3:40
+МН</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="6"/>
+        <rFont val="Arial Narrow"/>
+      </rPr>
+      <t>3:40</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <rFont val="Arial Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+*</t>
+    </r>
+  </si>
+  <si>
+    <t>63У</t>
+  </si>
+  <si>
+    <t>62У</t>
+  </si>
+  <si>
     <t>ЩЕ</t>
   </si>
   <si>
-    <t>1:30
-ЩЕ</t>
+    <t>4:10</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t>1:50</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>7:30</t>
+  </si>
+  <si>
+    <t>Д63</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>9:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6458 - 6463 - 6650 - 6663</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н63</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6668 - 7731</t>
+  </si>
+  <si>
+    <t>2:00</t>
+  </si>
+  <si>
+    <t>6:15</t>
+  </si>
+  <si>
+    <t>4:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>2:00
+МЯ</t>
   </si>
   <si>
     <r>
@@ -1050,218 +1262,6 @@
     </r>
   </si>
   <si>
-    <t>62У</t>
-  </si>
-  <si>
-    <t>61У</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>2:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6002 - 6007</t>
-  </si>
-  <si>
-    <t>7:45</t>
-  </si>
-  <si>
-    <t>5:15</t>
-  </si>
-  <si>
-    <t>3:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t>Д62</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>6:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6454 - 6459 - 6834 - 6839</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>9:55</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н62</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>3:40</t>
-  </si>
-  <si>
-    <t>5:10</t>
-  </si>
-  <si>
-    <t>5:10</t>
-  </si>
-  <si>
-    <t>МН</t>
-  </si>
-  <si>
-    <t>3:40
-МН</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6"/>
-        <rFont val="Arial Narrow"/>
-      </rPr>
-      <t>3:40</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Arial Narrow"/>
-      </rPr>
-      <t xml:space="preserve">
-*</t>
-    </r>
-  </si>
-  <si>
-    <t>63У</t>
-  </si>
-  <si>
-    <t>62У</t>
-  </si>
-  <si>
-    <t>ЩЕ</t>
-  </si>
-  <si>
-    <t>3:30</t>
-  </si>
-  <si>
-    <t>7:40</t>
-  </si>
-  <si>
-    <t>4:10</t>
-  </si>
-  <si>
-    <t>2:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>7:30</t>
-  </si>
-  <si>
-    <t>Д63</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6458 - 6463 - 6650 - 6663</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н63</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6668 - 7731</t>
-  </si>
-  <si>
-    <t>2:00</t>
-  </si>
-  <si>
-    <t>6:15</t>
-  </si>
-  <si>
-    <t>4:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>2:00
-МЯ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="6"/>
-        <rFont val="Arial Narrow"/>
-      </rPr>
-      <t>3:30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <rFont val="Arial Narrow"/>
-      </rPr>
-      <t xml:space="preserve">
-**</t>
-    </r>
-  </si>
-  <si>
     <t>64У</t>
   </si>
   <si>
@@ -1550,16 +1550,17 @@
     <t>МЯ</t>
   </si>
   <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 80 мар. 6648 - 6681</t>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 88 мар. 6238 - 6251;
+принимают состав 80 мар. 6670 - 6681</t>
   </si>
   <si>
     <t>1:10</t>
   </si>
   <si>
-    <t>9:10</t>
+    <t>9:50</t>
   </si>
   <si>
     <t>3:10</t>
@@ -1605,80 +1606,82 @@
     <t>резерв</t>
   </si>
   <si>
+    <t>3:20</t>
+  </si>
+  <si>
+    <t>2:10</t>
+  </si>
+  <si>
+    <t>2:10</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>5:20</t>
+  </si>
+  <si>
+    <t>Д75</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 85 мар. 6630 - 6643, состав сдают по смене;
+принимают состав 62 мар. 6710 - 6715 - 6862 - 6863</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:50
+МЯ</t>
+  </si>
+  <si>
+    <t>15:50
+**</t>
+  </si>
+  <si>
+    <t>1:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н75</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 87 мар. 6648 - 7733</t>
+  </si>
+  <si>
+    <t>2:00</t>
+  </si>
+  <si>
+    <t>9:40</t>
+  </si>
+  <si>
     <t>4:00</t>
   </si>
   <si>
-    <t>2:50</t>
-  </si>
-  <si>
-    <t>2:50</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t>Д75</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>6:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 83 мар. 6614 - 6629, состав сдают по смене;
-принимают состав 85 мар. 6630 - 6643</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>8:40</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н75</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 62 мар. 6710 - 6715 - 6862 - 6863</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>8:10</t>
-  </si>
-  <si>
-    <t>1:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>23:30
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>2:00
 МЯ</t>
   </si>
   <si>
@@ -1688,7 +1691,7 @@
         <sz val="6"/>
         <rFont val="Arial Narrow"/>
       </rPr>
-      <t>0:00</t>
+      <t>2:00</t>
     </r>
     <r>
       <rPr>
@@ -1706,31 +1709,31 @@
     <t>75У</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>8:10</t>
-  </si>
-  <si>
-    <t>1:30</t>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>2:00</t>
+  </si>
+  <si>
+    <t>резерв</t>
+  </si>
+  <si>
+    <t>4:20</t>
+  </si>
+  <si>
+    <t>2:20</t>
+  </si>
+  <si>
+    <t>2:20</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>6:20</t>
   </si>
   <si>
     <t>Д76</t>
@@ -1773,7 +1776,7 @@
     <t>15:50</t>
   </si>
   <si>
-    <t xml:space="preserve">состав 79 мар. 6568 - 6577 - 6070 - 6081</t>
+    <t xml:space="preserve">состав 79 мар. 6568 - 6577 - 6070 - 6095</t>
   </si>
   <si>
     <t>1:00</t>
@@ -2083,7 +2086,7 @@
     <t>23:40</t>
   </si>
   <si>
-    <t xml:space="preserve">приёмка состава от п.6081</t>
+    <t xml:space="preserve">приёмка состава от п.6095</t>
   </si>
   <si>
     <t>3:00</t>
@@ -2145,24 +2148,24 @@
     <t>8:40</t>
   </si>
   <si>
-    <t xml:space="preserve">6826 - 6831 - 6564 - 6563; состав 93 мар. 6858 - 6859</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>16:30
-МЯ</t>
-  </si>
-  <si>
-    <t>18:20
+    <t xml:space="preserve">6826 - 6831 - 6690 - 7668 - 7669 - 6689</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>16:10
+ФВ</t>
+  </si>
+  <si>
+    <t>17:10
 **</t>
   </si>
   <si>
-    <t>0:30</t>
+    <t>0:00</t>
   </si>
   <si>
     <t>МЯ</t>
@@ -2432,16 +2435,16 @@
     <t>МЯ</t>
   </si>
   <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">принимают состав от п.6629, 6638 - 6653 - 6852 - 6855</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>11:10</t>
+    <t>6:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6614 - 6653</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>11:30</t>
   </si>
   <si>
     <t/>
@@ -2465,167 +2468,928 @@
     <t>20:20</t>
   </si>
   <si>
-    <t>1:50</t>
-  </si>
-  <si>
-    <t>5:30</t>
-  </si>
-  <si>
-    <t>3:50</t>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>5:00</t>
   </si>
   <si>
     <t>МН</t>
   </si>
   <si>
-    <t>1:50
+    <t>3:00
 МН</t>
+  </si>
+  <si>
+    <t>3:00
+*</t>
+  </si>
+  <si>
+    <t>84У</t>
+  </si>
+  <si>
+    <t>83У</t>
+  </si>
+  <si>
+    <t>ПУ</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7702 - 6703</t>
+  </si>
+  <si>
+    <t>7:50</t>
+  </si>
+  <si>
+    <t>4:20</t>
+  </si>
+  <si>
+    <t>2:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t>Д84</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>8:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6624 - 6637 - 6850 - 6853</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>15:00
+МЯ</t>
+  </si>
+  <si>
+    <t>16:00
+**</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н84</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>1:00</t>
+  </si>
+  <si>
+    <t>5:00</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>ПУ</t>
+  </si>
+  <si>
+    <t>1:00
+ПУ</t>
   </si>
   <si>
     <t>3:00
 **</t>
   </si>
   <si>
+    <t>85У</t>
+  </si>
+  <si>
     <t>84У</t>
   </si>
   <si>
-    <t>83У</t>
+    <t>МН</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6601, состав сдают по смене под п.6008</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t>5:00</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>6:00</t>
+  </si>
+  <si>
+    <t>Д85</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>7:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6208 - 6221, состав сдают по смене;
+принимают состав от п.6643, 6640 - 6665</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>12:00
+МЯ</t>
+  </si>
+  <si>
+    <t>14:00
+**</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н85</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6866 - 6867</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>6:45</t>
+  </si>
+  <si>
+    <t>5:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>3:00
+МЯ</t>
+  </si>
+  <si>
+    <t>3:00
+*</t>
+  </si>
+  <si>
+    <t>86У</t>
+  </si>
+  <si>
+    <t>85У</t>
   </si>
   <si>
     <t>ПУ</t>
   </si>
   <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7632 - 6205 - 6556 - 6555</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>7:00</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t>Д86</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>7:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6618 - 6641 - 6844 - 6847</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н86</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6474 - 6479 - 6522</t>
+  </si>
+  <si>
+    <t>2:20</t>
+  </si>
+  <si>
+    <t>8:30</t>
+  </si>
+  <si>
+    <t>4:20</t>
+  </si>
+  <si>
+    <t>БО</t>
+  </si>
+  <si>
+    <t>2:20
+БО</t>
+  </si>
+  <si>
+    <t>3:40
+**</t>
+  </si>
+  <si>
+    <t>87У</t>
+  </si>
+  <si>
+    <t>86У</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6902 - 6901</t>
+  </si>
+  <si>
+    <t>7:40</t>
+  </si>
+  <si>
+    <t>4:40</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>6:40</t>
+  </si>
+  <si>
+    <t>Д87</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>8:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6822 - 6827, состав сдают по смене;
+принимают состав 83 мар. 6852 - 6855</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>14:10
+МЯ</t>
+  </si>
+  <si>
+    <t>15:40
+**</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н87</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
     <t>3:30</t>
   </si>
   <si>
-    <t xml:space="preserve">7702 - 6703</t>
-  </si>
-  <si>
-    <t>7:50</t>
-  </si>
-  <si>
-    <t>4:20</t>
-  </si>
-  <si>
-    <t>2:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
+    <t>3:40</t>
+  </si>
+  <si>
+    <t>3:40</t>
+  </si>
+  <si>
+    <t>БО</t>
+  </si>
+  <si>
+    <t>3:30
+БО</t>
+  </si>
+  <si>
+    <t>3:30
+*</t>
+  </si>
+  <si>
+    <t>88У</t>
+  </si>
+  <si>
+    <t>87У</t>
+  </si>
+  <si>
+    <t>БО</t>
+  </si>
+  <si>
+    <t>3:40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 88 мар. 6501</t>
+  </si>
+  <si>
+    <t>7:10</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t>2:20</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>9:10</t>
+  </si>
+  <si>
+    <t>6:10</t>
+  </si>
+  <si>
+    <t>Д88</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>9:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6460 - 6465, состав сдают по смене;
+принимают состав 93 мар. 6858 - 6859</t>
+  </si>
+  <si>
+    <t>22:30</t>
   </si>
   <si>
     <t>12:00</t>
   </si>
   <si>
-    <t>6:50</t>
-  </si>
-  <si>
-    <t>Д84</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>8:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6624 - 6637 - 6850 - 6853</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>15:00
+    <t>16:45
 МЯ</t>
   </si>
   <si>
-    <t>16:00
+    <t>17:45
 **</t>
   </si>
   <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н84</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>20:00</t>
+    <t>0:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н88</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6662 - 7711</t>
   </si>
   <si>
     <t>1:00</t>
   </si>
   <si>
-    <t>5:00</t>
+    <t>6:05</t>
   </si>
   <si>
     <t>3:00</t>
   </si>
   <si>
-    <t>ПУ</t>
+    <t>БО</t>
   </si>
   <si>
     <t>1:00
-ПУ</t>
+БО</t>
   </si>
   <si>
     <t>3:00
 **</t>
   </si>
   <si>
-    <t>85У</t>
-  </si>
-  <si>
-    <t>84У</t>
-  </si>
-  <si>
-    <t>МН</t>
+    <t>89У</t>
+  </si>
+  <si>
+    <t>88У</t>
+  </si>
+  <si>
+    <t>БО</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 87 мар. 7738 - 6615</t>
+  </si>
+  <si>
+    <t>9:00</t>
+  </si>
+  <si>
+    <t>5:30</t>
+  </si>
+  <si>
+    <t>2:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>6:00</t>
+  </si>
+  <si>
+    <t>Д89</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>8:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6214 - 6227 - 6226 - 6239 - 6848 - 6851</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н89</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">приёмка состава от п.6851</t>
+  </si>
+  <si>
+    <t>1:30</t>
+  </si>
+  <si>
+    <t>6:10</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>1:30
+МЯ</t>
+  </si>
+  <si>
+    <t>3:30
+**</t>
+  </si>
+  <si>
+    <t>90У</t>
+  </si>
+  <si>
+    <t>89У</t>
+  </si>
+  <si>
+    <t>БО</t>
   </si>
   <si>
     <t>3:00</t>
   </si>
   <si>
-    <t xml:space="preserve">6601 - 6504 - 6503</t>
-  </si>
-  <si>
-    <t>9:30</t>
+    <t xml:space="preserve">7736 - 6453</t>
+  </si>
+  <si>
+    <t>8:55</t>
+  </si>
+  <si>
+    <t>5:55</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>6:00</t>
+  </si>
+  <si>
+    <t>Д90</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>7:50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6016 - 6093 - 6468 - 6473</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>11:40
+ПУ</t>
+  </si>
+  <si>
+    <t>13:20
+**</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н90</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>2:00</t>
+  </si>
+  <si>
+    <t>5:35</t>
+  </si>
+  <si>
+    <t>4:00</t>
+  </si>
+  <si>
+    <t>ПУ</t>
+  </si>
+  <si>
+    <t>2:00
+ПУ</t>
+  </si>
+  <si>
+    <t>3:00
+**</t>
+  </si>
+  <si>
+    <t>76У</t>
+  </si>
+  <si>
+    <t>90У</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6702 - 6705</t>
+  </si>
+  <si>
+    <t>9:20</t>
+  </si>
+  <si>
+    <t>5:50</t>
+  </si>
+  <si>
+    <t>2:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>7:00</t>
+  </si>
+  <si>
+    <t>Д91</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>9:10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 81 мар. 6560 - 6559, состав сдают по смене;
+принимают состав 58 мар. 6110 - 6067</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н91</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>0:00
+*</t>
+  </si>
+  <si>
+    <t>92У</t>
+  </si>
+  <si>
+    <t>91У</t>
+  </si>
+  <si>
+    <t>ПУ</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 92 мар. 6005</t>
+  </si>
+  <si>
+    <t>7:30</t>
+  </si>
+  <si>
+    <t>4:30</t>
+  </si>
+  <si>
+    <t>3:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>Д92</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>8:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">пасс. до ст. Пушкино, 6047 - 6466 - 6471</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>Н92</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>4:00</t>
+  </si>
+  <si>
+    <t>8:30</t>
+  </si>
+  <si>
+    <t>6:00</t>
+  </si>
+  <si>
+    <t>ПУ</t>
+  </si>
+  <si>
+    <t>4:00
+ПУ</t>
+  </si>
+  <si>
+    <t>5:30
+**</t>
+  </si>
+  <si>
+    <t>93У</t>
+  </si>
+  <si>
+    <t>92У</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>12:00</t>
   </si>
   <si>
     <t>6:30</t>
   </si>
   <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>12:00</t>
+    <t>Д93</t>
+  </si>
+  <si>
+    <t>МЯ</t>
   </si>
   <si>
     <t>6:00</t>
   </si>
   <si>
-    <t>Д85</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>7:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6208 - 6221, состав сдают по смене;
-принимают состав от п.6643, 6640 - 6665</t>
-  </si>
-  <si>
-    <t>21:20</t>
+    <t xml:space="preserve">пасс. до ПУ, 6025; 6642 - 6655</t>
+  </si>
+  <si>
+    <t>19:00</t>
   </si>
   <si>
     <t>12:00</t>
@@ -2635,7 +3399,7 @@
 МЯ</t>
   </si>
   <si>
-    <t>14:00
+    <t>13:00
 **</t>
   </si>
   <si>
@@ -2645,842 +3409,81 @@
     <t>МЯ</t>
   </si>
   <si>
-    <t>Н85</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6866 - 6867</t>
+    <t>Н93</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>22:00</t>
   </si>
   <si>
     <t>3:00</t>
   </si>
   <si>
-    <t>6:45</t>
-  </si>
-  <si>
     <t>5:00</t>
   </si>
   <si>
-    <t>МЯ</t>
+    <t>5:00</t>
+  </si>
+  <si>
+    <t>МН</t>
   </si>
   <si>
     <t>3:00
-МЯ</t>
+МН</t>
   </si>
   <si>
     <t>3:00
 *</t>
   </si>
   <si>
-    <t>86У</t>
-  </si>
-  <si>
-    <t>85У</t>
+    <t>94У</t>
+  </si>
+  <si>
+    <t>93У</t>
   </si>
   <si>
     <t>ПУ</t>
   </si>
   <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7632 - 6205 - 6556 - 6555</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>7:00</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>11:25</t>
+    <t>5:30</t>
+  </si>
+  <si>
+    <t>9:00</t>
+  </si>
+  <si>
+    <t>3:30</t>
+  </si>
+  <si>
+    <t>0:30</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>11:00</t>
   </si>
   <si>
     <t>8:00</t>
   </si>
   <si>
-    <t>Д86</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>7:45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6618 - 6641 - 6844 - 6847</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н86</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6474 - 6479 - 6522</t>
-  </si>
-  <si>
-    <t>2:20</t>
-  </si>
-  <si>
-    <t>8:30</t>
-  </si>
-  <si>
-    <t>4:20</t>
-  </si>
-  <si>
-    <t>БО</t>
-  </si>
-  <si>
-    <t>2:20
-БО</t>
-  </si>
-  <si>
-    <t>3:40
-**</t>
-  </si>
-  <si>
-    <t>87У</t>
-  </si>
-  <si>
-    <t>86У</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6902 - 6901</t>
-  </si>
-  <si>
-    <t>7:40</t>
-  </si>
-  <si>
-    <t>4:40</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>6:40</t>
-  </si>
-  <si>
-    <t>Д87</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6822 - 6827, состав сдают по смене;
-принимают состав от п.6649, 6570 - 6569</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>14:10
-МЯ</t>
-  </si>
-  <si>
-    <t>15:20
-**</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н87</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6670 - 7733 - 7734</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>6:50</t>
-  </si>
-  <si>
-    <t>5:00</t>
-  </si>
-  <si>
-    <t>БО</t>
-  </si>
-  <si>
-    <t>3:00
-БО</t>
-  </si>
-  <si>
-    <t>4:00
-**</t>
-  </si>
-  <si>
-    <t>88У</t>
-  </si>
-  <si>
-    <t>87У</t>
-  </si>
-  <si>
-    <t>БО</t>
-  </si>
-  <si>
-    <t>3:40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 88 мар. 6501</t>
-  </si>
-  <si>
-    <t>7:10</t>
-  </si>
-  <si>
-    <t>3:30</t>
-  </si>
-  <si>
-    <t>2:20</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>7:00</t>
-  </si>
-  <si>
-    <t>Д88</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>9:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6460 - 6465 - 6238 - 6251</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н88</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6662 - 7711</t>
-  </si>
-  <si>
-    <t>1:00</t>
-  </si>
-  <si>
-    <t>6:05</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>БО</t>
-  </si>
-  <si>
-    <t>1:00
-БО</t>
-  </si>
-  <si>
-    <t>3:00
-**</t>
-  </si>
-  <si>
-    <t>89У</t>
-  </si>
-  <si>
-    <t>88У</t>
-  </si>
-  <si>
-    <t>БО</t>
-  </si>
-  <si>
-    <t>4:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 87 мар. 7738 - 6615</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t>5:00</t>
-  </si>
-  <si>
-    <t>2:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t>Д89</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>8:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6214 - 6227 - 6226 - 6239 - 6848 - 6851</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н89</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">приёмка состава от п.6851</t>
-  </si>
-  <si>
-    <t>1:30</t>
-  </si>
-  <si>
-    <t>6:10</t>
-  </si>
-  <si>
-    <t>3:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>1:30
-МЯ</t>
-  </si>
-  <si>
-    <t>3:30
-**</t>
-  </si>
-  <si>
-    <t>90У</t>
-  </si>
-  <si>
-    <t>89У</t>
-  </si>
-  <si>
-    <t>БО</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7736 - 6453</t>
-  </si>
-  <si>
-    <t>8:55</t>
-  </si>
-  <si>
-    <t>5:55</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t>Д90</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>7:50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6016 - 6053 - 6468 - 6473</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>11:40
-ПУ</t>
-  </si>
-  <si>
-    <t>13:20
-**</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н90</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>2:00</t>
-  </si>
-  <si>
-    <t>5:35</t>
-  </si>
-  <si>
-    <t>4:00</t>
-  </si>
-  <si>
-    <t>ПУ</t>
-  </si>
-  <si>
-    <t>2:00
-ПУ</t>
-  </si>
-  <si>
-    <t>3:00
-**</t>
-  </si>
-  <si>
-    <t>76У</t>
-  </si>
-  <si>
-    <t>90У</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>3:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6702 - 6705</t>
-  </si>
-  <si>
-    <t>9:20</t>
-  </si>
-  <si>
-    <t>5:50</t>
-  </si>
-  <si>
-    <t>2:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
+    <t>Д94</t>
+  </si>
+  <si>
+    <t>МЯ</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">состав 93м 6220 - 6235; 6854 - 6857</t>
+  </si>
+  <si>
+    <t>22:00</t>
   </si>
   <si>
     <t>11:35</t>
-  </si>
-  <si>
-    <t>7:00</t>
-  </si>
-  <si>
-    <t>Д91</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>9:10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 81 мар. 6560 - 6559, состав сдают по смене;
-принимают состав 92 мар. 6466 - 6471</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н91</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>0:00
-*</t>
-  </si>
-  <si>
-    <t>92У</t>
-  </si>
-  <si>
-    <t>91У</t>
-  </si>
-  <si>
-    <t>ПУ</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 92 мар. 6005</t>
-  </si>
-  <si>
-    <t>7:30</t>
-  </si>
-  <si>
-    <t>4:30</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>Д92</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>6:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6816 - 6821 - 6028 - 6047</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>9:05</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н92</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>4:00</t>
-  </si>
-  <si>
-    <t>8:30</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t>ПУ</t>
-  </si>
-  <si>
-    <t>4:00
-ПУ</t>
-  </si>
-  <si>
-    <t>5:30
-**</t>
-  </si>
-  <si>
-    <t>93У</t>
-  </si>
-  <si>
-    <t>92У</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>6:30</t>
-  </si>
-  <si>
-    <t>Д93</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>6:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">пасс. до ПУ, 6025; 6642 - 6655</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:00
-МЯ</t>
-  </si>
-  <si>
-    <t>13:00
-**</t>
-  </si>
-  <si>
-    <t>0:00</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>Н93</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>3:00</t>
-  </si>
-  <si>
-    <t>5:00</t>
-  </si>
-  <si>
-    <t>5:00</t>
-  </si>
-  <si>
-    <t>МН</t>
-  </si>
-  <si>
-    <t>3:00
-МН</t>
-  </si>
-  <si>
-    <t>3:00
-*</t>
-  </si>
-  <si>
-    <t>94У</t>
-  </si>
-  <si>
-    <t>93У</t>
-  </si>
-  <si>
-    <t>ПУ</t>
-  </si>
-  <si>
-    <t>5:30</t>
-  </si>
-  <si>
-    <t>9:00</t>
-  </si>
-  <si>
-    <t>3:30</t>
-  </si>
-  <si>
-    <t>0:30</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>8:00</t>
-  </si>
-  <si>
-    <t>Д94</t>
-  </si>
-  <si>
-    <t>МЯ</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">состав 93м 6220 - 6235; 6854 - 6857</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
   </si>
   <si>
     <t/>
@@ -4665,7 +4668,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="21">
+  <fonts count="23" x14ac:knownFonts="23">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -4690,13 +4693,25 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="7"/>
       <name val="Times New Roman"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="8.5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -4783,12 +4798,30 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7DEE8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="13">
@@ -4937,254 +4970,341 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="left"/>
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment wrapText="1" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1" horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5492,13 +5612,13 @@
     <col min="20" max="20" width="4"/>
     <col min="21" max="21" width="17"/>
     <col min="22" max="22" width="17"/>
-    <col min="23" max="23" width="16"/>
+    <col min="23" max="23" width="17"/>
     <col min="24" max="24" width="3"/>
     <col min="25" max="25" width="39"/>
-    <col min="26" max="26" width="17"/>
+    <col min="26" max="26" width="18"/>
     <col min="27" max="27" width="19"/>
     <col min="28" max="28" width="3"/>
-    <col min="29" max="29" width="16"/>
+    <col min="29" max="29" width="17"/>
     <col min="30" max="30" width="4"/>
     <col min="31" max="31" width="3"/>
   </cols>
@@ -5513,7 +5633,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="0" t="s">
@@ -5590,13 +5710,13 @@
       <c r="A2" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="0" t="s">
@@ -5669,17 +5789,17 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25" ht="10" customHeight="1">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25" ht="11" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E3" s="6" t="s">
@@ -5753,4137 +5873,4137 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25" ht="10" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="L4" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="M4" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="N4" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="O4" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="P4" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="Q4" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="R4" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="S4" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="T4" s="11" t="s">
+      <c r="T4" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="U4" s="13" t="s">
+      <c r="U4" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="W4" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="X4" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="Y4" s="12" t="s">
+      <c r="Y4" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="Z4" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="AA4" s="9" t="s">
+      <c r="AA4" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="AB4" s="9" t="s">
+      <c r="AB4" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="AC4" s="11" t="s">
+      <c r="AC4" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AD4" s="14" t="s">
+      <c r="AD4" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="AE4" s="11" t="s">
+      <c r="AE4" s="13" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25" ht="60" customHeight="1">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="H5" s="18" t="s">
+      <c r="H5" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="O5" s="20" t="s">
+      <c r="O5" s="22" t="s">
         <v>126</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="R5" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="S5" s="17" t="s">
+      <c r="S5" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="T5" s="18" t="s">
+      <c r="T5" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="U5" s="21" t="s">
+      <c r="U5" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="V5" s="15" t="s">
+      <c r="V5" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="W5" s="15" t="s">
+      <c r="W5" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="X5" s="22" t="s">
+      <c r="X5" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="Y5" s="19" t="s">
+      <c r="Y5" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="Z5" s="20" t="s">
+      <c r="Z5" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="AA5" s="15" t="s">
+      <c r="AA5" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="AB5" s="15" t="s">
+      <c r="AB5" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="AC5" s="15" t="s">
+      <c r="AC5" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="AD5" s="15" t="s">
+      <c r="AD5" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="AE5" s="15" t="s">
+      <c r="AE5" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="G6" s="26" t="s">
+      <c r="G6" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="H6" s="29" t="s">
         <v>150</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="J6" s="16" t="s">
+      <c r="J6" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="M6" s="23" t="s">
+      <c r="M6" s="25" t="s">
         <v>155</v>
       </c>
-      <c r="N6" s="24" t="s">
+      <c r="N6" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="O6" s="16" t="s">
+      <c r="O6" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="P6" s="25" t="s">
+      <c r="P6" s="27" t="s">
         <v>158</v>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="27" t="s">
         <v>159</v>
       </c>
-      <c r="R6" s="23" t="s">
+      <c r="R6" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="S6" s="26" t="s">
+      <c r="S6" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="T6" s="27" t="s">
+      <c r="T6" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="U6" s="29" t="s">
+      <c r="U6" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="V6" s="23" t="s">
+      <c r="V6" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="W6" s="23" t="s">
+      <c r="W6" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="X6" s="16" t="s">
+      <c r="X6" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="Y6" s="24" t="s">
+      <c r="Y6" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="Z6" s="23" t="s">
+      <c r="Z6" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="AA6" s="25" t="s">
+      <c r="AA6" s="27" t="s">
         <v>169</v>
       </c>
-      <c r="AB6" s="29" t="s">
+      <c r="AB6" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="AC6" s="23" t="s">
+      <c r="AC6" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="AD6" s="23" t="s">
+      <c r="AD6" s="25" t="s">
         <v>172</v>
       </c>
-      <c r="AE6" s="29" t="s">
+      <c r="AE6" s="31" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25" ht="17" customHeight="1">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="32" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="D7" s="16" t="s">
+      <c r="D7" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="35" t="s">
         <v>179</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="H7" s="32" t="s">
+      <c r="H7" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="I7" s="28" t="s">
+      <c r="I7" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="J7" s="16" t="s">
+      <c r="J7" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="18">
         <v>6678</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O7" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="27" t="s">
         <v>188</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="23" t="s">
+      <c r="R7" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="S7" s="26" t="s">
+      <c r="S7" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="T7" s="27" t="s">
+      <c r="T7" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="U7" s="29" t="s">
+      <c r="U7" s="31" t="s">
         <v>193</v>
       </c>
-      <c r="V7" s="23" t="s">
+      <c r="V7" s="25" t="s">
         <v>194</v>
       </c>
-      <c r="W7" s="23" t="s">
+      <c r="W7" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="X7" s="16" t="s">
+      <c r="X7" s="18" t="s">
         <v>196</v>
       </c>
-      <c r="Y7" s="16">
+      <c r="Y7" s="18">
         <v>6009</v>
       </c>
-      <c r="Z7" s="23" t="s">
+      <c r="Z7" s="25" t="s">
         <v>197</v>
       </c>
-      <c r="AA7" s="25" t="s">
+      <c r="AA7" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="AB7" s="29" t="s">
+      <c r="AB7" s="31" t="s">
         <v>199</v>
       </c>
-      <c r="AC7" s="23" t="s">
+      <c r="AC7" s="25" t="s">
         <v>200</v>
       </c>
-      <c r="AD7" s="23" t="s">
+      <c r="AD7" s="25" t="s">
         <v>201</v>
       </c>
-      <c r="AE7" s="29" t="s">
+      <c r="AE7" s="31" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="40" t="s">
         <v>204</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="F8" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="G8" s="26" t="s">
+      <c r="G8" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="H8" s="27" t="s">
+      <c r="H8" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="46" t="s">
         <v>211</v>
       </c>
-      <c r="J8" s="16" t="s">
+      <c r="J8" s="41" t="s">
         <v>212</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="L8" s="23" t="s">
+      <c r="L8" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="N8" s="16" t="s">
+      <c r="N8" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="O8" s="16" t="s">
+      <c r="O8" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="P8" s="25" t="s">
+      <c r="P8" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="Q8" s="25" t="s">
+      <c r="Q8" s="27" t="s">
         <v>219</v>
       </c>
-      <c r="R8" s="23" t="s">
+      <c r="R8" s="25" t="s">
         <v>220</v>
       </c>
-      <c r="S8" s="26" t="s">
+      <c r="S8" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="T8" s="27" t="s">
+      <c r="T8" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="U8" s="29" t="s">
+      <c r="U8" s="31" t="s">
         <v>223</v>
       </c>
-      <c r="V8" s="23" t="s">
+      <c r="V8" s="25" t="s">
         <v>224</v>
       </c>
-      <c r="W8" s="23" t="s">
+      <c r="W8" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="X8" s="16" t="s">
+      <c r="X8" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="Y8" s="16">
+      <c r="Y8" s="18">
         <v>6613</v>
       </c>
-      <c r="Z8" s="23" t="s">
+      <c r="Z8" s="25" t="s">
         <v>227</v>
       </c>
-      <c r="AA8" s="25" t="s">
+      <c r="AA8" s="27" t="s">
         <v>228</v>
       </c>
-      <c r="AB8" s="29" t="s">
+      <c r="AB8" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="AC8" s="23" t="s">
+      <c r="AC8" s="25" t="s">
         <v>230</v>
       </c>
-      <c r="AD8" s="23" t="s">
+      <c r="AD8" s="25" t="s">
         <v>231</v>
       </c>
-      <c r="AE8" s="29" t="s">
+      <c r="AE8" s="31" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25" ht="17" customHeight="1">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="27" t="s">
         <v>238</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="H9" s="32" t="s">
+      <c r="H9" s="49" t="s">
         <v>240</v>
       </c>
-      <c r="I9" s="28" t="s">
+      <c r="I9" s="30" t="s">
         <v>241</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="J9" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="40" t="s">
         <v>243</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="L9" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="40" t="s">
         <v>245</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="41" t="s">
         <v>246</v>
       </c>
-      <c r="O9" s="16" t="s">
+      <c r="O9" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="P9" s="25" t="s">
+      <c r="P9" s="43" t="s">
         <v>248</v>
       </c>
-      <c r="Q9" s="25" t="s">
+      <c r="Q9" s="43" t="s">
         <v>249</v>
       </c>
-      <c r="R9" s="23" t="s">
+      <c r="R9" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="S9" s="26" t="s">
+      <c r="S9" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="T9" s="27" t="s">
+      <c r="T9" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="U9" s="29" t="s">
+      <c r="U9" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="V9" s="23" t="s">
+      <c r="V9" s="25" t="s">
         <v>254</v>
       </c>
-      <c r="W9" s="23" t="s">
+      <c r="W9" s="25" t="s">
         <v>255</v>
       </c>
-      <c r="X9" s="16" t="s">
+      <c r="X9" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="Y9" s="16" t="s">
+      <c r="Y9" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="Z9" s="23" t="s">
+      <c r="Z9" s="25" t="s">
         <v>258</v>
       </c>
-      <c r="AA9" s="25" t="s">
+      <c r="AA9" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="AB9" s="29" t="s">
+      <c r="AB9" s="31" t="s">
         <v>260</v>
       </c>
-      <c r="AC9" s="23" t="s">
+      <c r="AC9" s="25" t="s">
         <v>261</v>
       </c>
-      <c r="AD9" s="23" t="s">
+      <c r="AD9" s="25" t="s">
         <v>262</v>
       </c>
-      <c r="AE9" s="29" t="s">
+      <c r="AE9" s="31" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25" ht="17" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="47" t="s">
         <v>264</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="18" t="s">
         <v>267</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="27" t="s">
         <v>269</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="49" t="s">
         <v>271</v>
       </c>
-      <c r="I10" s="28" t="s">
+      <c r="I10" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="J10" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="40" t="s">
         <v>274</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="40" t="s">
         <v>275</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="N10" s="24" t="s">
+      <c r="N10" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="O10" s="16" t="s">
+      <c r="O10" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="P10" s="25" t="s">
+      <c r="P10" s="43" t="s">
         <v>279</v>
       </c>
-      <c r="Q10" s="25" t="s">
+      <c r="Q10" s="43" t="s">
         <v>280</v>
       </c>
-      <c r="R10" s="23" t="s">
+      <c r="R10" s="40" t="s">
         <v>281</v>
       </c>
-      <c r="S10" s="26" t="s">
+      <c r="S10" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="T10" s="27" t="s">
+      <c r="T10" s="45" t="s">
         <v>283</v>
       </c>
-      <c r="U10" s="29" t="s">
+      <c r="U10" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="V10" s="23" t="s">
+      <c r="V10" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="W10" s="23" t="s">
+      <c r="W10" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="X10" s="16" t="s">
+      <c r="X10" s="41" t="s">
         <v>287</v>
       </c>
-      <c r="Y10" s="16" t="s">
+      <c r="Y10" s="41" t="s">
         <v>288</v>
       </c>
-      <c r="Z10" s="23" t="s">
+      <c r="Z10" s="40" t="s">
         <v>289</v>
       </c>
-      <c r="AA10" s="25" t="s">
+      <c r="AA10" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="AB10" s="29" t="s">
+      <c r="AB10" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="AC10" s="23" t="s">
+      <c r="AC10" s="40" t="s">
         <v>292</v>
       </c>
-      <c r="AD10" s="23" t="s">
+      <c r="AD10" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="AE10" s="29" t="s">
+      <c r="AE10" s="31" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25" ht="17" customHeight="1">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="47" t="s">
         <v>295</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="25" t="s">
         <v>299</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="48" t="s">
         <v>301</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="49" t="s">
         <v>302</v>
       </c>
-      <c r="I11" s="28" t="s">
+      <c r="I11" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="18" t="s">
         <v>304</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="L11" s="23" t="s">
+      <c r="L11" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="18">
         <v>6680</v>
       </c>
-      <c r="O11" s="16" t="s">
+      <c r="O11" s="18" t="s">
         <v>308</v>
       </c>
-      <c r="P11" s="25" t="s">
+      <c r="P11" s="27" t="s">
         <v>309</v>
       </c>
-      <c r="Q11" s="25" t="s">
+      <c r="Q11" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="R11" s="23" t="s">
+      <c r="R11" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="S11" s="26" t="s">
+      <c r="S11" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="T11" s="27" t="s">
+      <c r="T11" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="U11" s="29" t="s">
+      <c r="U11" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="V11" s="23" t="s">
+      <c r="V11" s="40" t="s">
         <v>315</v>
       </c>
-      <c r="W11" s="23" t="s">
+      <c r="W11" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="X11" s="16" t="s">
+      <c r="X11" s="41" t="s">
         <v>317</v>
       </c>
-      <c r="Y11" s="16">
+      <c r="Y11" s="41">
         <v>6551</v>
       </c>
-      <c r="Z11" s="23" t="s">
+      <c r="Z11" s="40" t="s">
         <v>318</v>
       </c>
-      <c r="AA11" s="25" t="s">
+      <c r="AA11" s="43" t="s">
         <v>319</v>
       </c>
-      <c r="AB11" s="29" t="s">
+      <c r="AB11" s="46" t="s">
         <v>320</v>
       </c>
-      <c r="AC11" s="23" t="s">
+      <c r="AC11" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="AD11" s="23" t="s">
+      <c r="AD11" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="AE11" s="29" t="s">
+      <c r="AE11" s="31" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25" ht="17" customHeight="1">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="47" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="25" t="s">
         <v>328</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="48" t="s">
         <v>330</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="I12" s="28" t="s">
+      <c r="I12" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="J12" s="16" t="s">
+      <c r="J12" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="25" t="s">
         <v>334</v>
       </c>
-      <c r="L12" s="23" t="s">
+      <c r="L12" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="25" t="s">
         <v>336</v>
       </c>
-      <c r="N12" s="16" t="s">
+      <c r="N12" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="O12" s="16" t="s">
+      <c r="O12" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="P12" s="25" t="s">
+      <c r="P12" s="27" t="s">
         <v>339</v>
       </c>
-      <c r="Q12" s="25" t="s">
+      <c r="Q12" s="27" t="s">
         <v>340</v>
       </c>
-      <c r="R12" s="23" t="s">
+      <c r="R12" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="S12" s="26" t="s">
+      <c r="S12" s="28" t="s">
         <v>342</v>
       </c>
-      <c r="T12" s="27" t="s">
+      <c r="T12" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="U12" s="29" t="s">
+      <c r="U12" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="V12" s="23" t="s">
+      <c r="V12" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="W12" s="23" t="s">
+      <c r="W12" s="25" t="s">
         <v>346</v>
       </c>
-      <c r="X12" s="16" t="s">
+      <c r="X12" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="Y12" s="16" t="s">
+      <c r="Y12" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="Z12" s="23" t="s">
+      <c r="Z12" s="25" t="s">
         <v>349</v>
       </c>
-      <c r="AA12" s="25" t="s">
+      <c r="AA12" s="27" t="s">
         <v>350</v>
       </c>
-      <c r="AB12" s="29" t="s">
+      <c r="AB12" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="AC12" s="23" t="s">
+      <c r="AC12" s="25" t="s">
         <v>352</v>
       </c>
-      <c r="AD12" s="23" t="s">
+      <c r="AD12" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="AE12" s="29" t="s">
+      <c r="AE12" s="31" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="47" t="s">
         <v>355</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="D13" s="33" t="s">
+      <c r="D13" s="50" t="s">
         <v>358</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="27" t="s">
         <v>360</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="48" t="s">
         <v>361</v>
       </c>
-      <c r="H13" s="32" t="s">
+      <c r="H13" s="49" t="s">
         <v>362</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="J13" s="16" t="s">
+      <c r="J13" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="K13" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="L13" s="23" t="s">
+      <c r="L13" s="25" t="s">
         <v>366</v>
       </c>
-      <c r="M13" s="23" t="s">
+      <c r="M13" s="25" t="s">
         <v>367</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="26" t="s">
         <v>368</v>
       </c>
-      <c r="O13" s="16" t="s">
+      <c r="O13" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="P13" s="25" t="s">
+      <c r="P13" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="Q13" s="25" t="s">
+      <c r="Q13" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="R13" s="23" t="s">
+      <c r="R13" s="25" t="s">
         <v>372</v>
       </c>
-      <c r="S13" s="26" t="s">
+      <c r="S13" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="T13" s="27" t="s">
+      <c r="T13" s="29" t="s">
         <v>374</v>
       </c>
-      <c r="U13" s="29" t="s">
+      <c r="U13" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="V13" s="23" t="s">
+      <c r="V13" s="25" t="s">
         <v>376</v>
       </c>
-      <c r="W13" s="23" t="s">
+      <c r="W13" s="25" t="s">
         <v>377</v>
       </c>
-      <c r="X13" s="16" t="s">
+      <c r="X13" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="Y13" s="16" t="s">
+      <c r="Y13" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="Z13" s="23" t="s">
+      <c r="Z13" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="AA13" s="25" t="s">
+      <c r="AA13" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="AB13" s="29" t="s">
+      <c r="AB13" s="31" t="s">
         <v>382</v>
       </c>
-      <c r="AC13" s="23" t="s">
+      <c r="AC13" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="AD13" s="23" t="s">
+      <c r="AD13" s="25" t="s">
         <v>384</v>
       </c>
-      <c r="AE13" s="29" t="s">
+      <c r="AE13" s="31" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="25" t="s">
         <v>387</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="26" t="s">
         <v>389</v>
       </c>
-      <c r="E14" s="23" t="s">
+      <c r="E14" s="25" t="s">
         <v>390</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="27" t="s">
         <v>391</v>
       </c>
-      <c r="G14" s="31" t="s">
+      <c r="G14" s="48" t="s">
         <v>392</v>
       </c>
-      <c r="H14" s="32" t="s">
+      <c r="H14" s="49" t="s">
         <v>393</v>
       </c>
-      <c r="I14" s="29" t="s">
+      <c r="I14" s="31" t="s">
         <v>394</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="K14" s="25" t="s">
         <v>396</v>
       </c>
-      <c r="L14" s="34" t="s">
+      <c r="L14" s="51" t="s">
         <v>397</v>
       </c>
-      <c r="M14" s="35" t="s">
+      <c r="M14" s="52" t="s">
         <v>398</v>
       </c>
-      <c r="N14" s="36" t="s">
+      <c r="N14" s="51" t="s">
         <v>399</v>
       </c>
-      <c r="O14" s="35" t="s">
+      <c r="O14" s="52" t="s">
         <v>400</v>
       </c>
-      <c r="P14" s="37" t="s">
+      <c r="P14" s="53" t="s">
         <v>401</v>
       </c>
-      <c r="Q14" s="37" t="s">
+      <c r="Q14" s="53" t="s">
         <v>402</v>
       </c>
-      <c r="R14" s="34" t="s">
+      <c r="R14" s="51" t="s">
         <v>403</v>
       </c>
-      <c r="S14" s="38" t="s">
+      <c r="S14" s="54" t="s">
         <v>404</v>
       </c>
-      <c r="T14" s="39" t="s">
+      <c r="T14" s="55" t="s">
         <v>405</v>
       </c>
-      <c r="U14" s="29" t="s">
+      <c r="U14" s="31" t="s">
         <v>406</v>
       </c>
-      <c r="V14" s="23" t="s">
+      <c r="V14" s="25" t="s">
         <v>407</v>
       </c>
-      <c r="W14" s="34" t="s">
+      <c r="W14" s="51" t="s">
         <v>408</v>
       </c>
-      <c r="X14" s="35" t="s">
+      <c r="X14" s="52" t="s">
         <v>409</v>
       </c>
-      <c r="Y14" s="36" t="s">
+      <c r="Y14" s="56" t="s">
         <v>410</v>
       </c>
-      <c r="Z14" s="40" t="s">
+      <c r="Z14" s="57" t="s">
         <v>411</v>
       </c>
-      <c r="AA14" s="37" t="s">
+      <c r="AA14" s="53" t="s">
         <v>412</v>
       </c>
-      <c r="AB14" s="28" t="s">
+      <c r="AB14" s="30" t="s">
         <v>413</v>
       </c>
-      <c r="AC14" s="34" t="s">
+      <c r="AC14" s="51" t="s">
         <v>414</v>
       </c>
-      <c r="AD14" s="40" t="s">
+      <c r="AD14" s="57" t="s">
         <v>415</v>
       </c>
-      <c r="AE14" s="28" t="s">
+      <c r="AE14" s="30" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="47" t="s">
         <v>417</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="25" t="s">
         <v>418</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="50" t="s">
         <v>420</v>
       </c>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="27" t="s">
         <v>422</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="48" t="s">
         <v>423</v>
       </c>
-      <c r="H15" s="32" t="s">
+      <c r="H15" s="49" t="s">
         <v>424</v>
       </c>
-      <c r="I15" s="28" t="s">
+      <c r="I15" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="J15" s="16" t="s">
+      <c r="J15" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="K15" s="40" t="s">
         <v>427</v>
       </c>
-      <c r="L15" s="23" t="s">
+      <c r="L15" s="40" t="s">
         <v>428</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="M15" s="40" t="s">
         <v>429</v>
       </c>
-      <c r="N15" s="24" t="s">
+      <c r="N15" s="58" t="s">
         <v>430</v>
       </c>
-      <c r="O15" s="16" t="s">
+      <c r="O15" s="41" t="s">
         <v>431</v>
       </c>
-      <c r="P15" s="25" t="s">
+      <c r="P15" s="43" t="s">
         <v>432</v>
       </c>
-      <c r="Q15" s="25" t="s">
+      <c r="Q15" s="43" t="s">
         <v>433</v>
       </c>
-      <c r="R15" s="23" t="s">
+      <c r="R15" s="40" t="s">
         <v>434</v>
       </c>
-      <c r="S15" s="26" t="s">
+      <c r="S15" s="44" t="s">
         <v>435</v>
       </c>
-      <c r="T15" s="27" t="s">
+      <c r="T15" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="U15" s="29" t="s">
+      <c r="U15" s="46" t="s">
         <v>437</v>
       </c>
-      <c r="V15" s="23" t="s">
+      <c r="V15" s="40" t="s">
         <v>438</v>
       </c>
-      <c r="W15" s="23" t="s">
+      <c r="W15" s="40" t="s">
         <v>439</v>
       </c>
-      <c r="X15" s="16" t="s">
+      <c r="X15" s="41" t="s">
         <v>440</v>
       </c>
-      <c r="Y15" s="24" t="s">
+      <c r="Y15" s="59" t="s">
         <v>441</v>
       </c>
-      <c r="Z15" s="23" t="s">
+      <c r="Z15" s="40" t="s">
         <v>442</v>
       </c>
-      <c r="AA15" s="25" t="s">
+      <c r="AA15" s="43" t="s">
         <v>443</v>
       </c>
-      <c r="AB15" s="29" t="s">
+      <c r="AB15" s="46" t="s">
         <v>444</v>
       </c>
-      <c r="AC15" s="23" t="s">
+      <c r="AC15" s="40" t="s">
         <v>445</v>
       </c>
-      <c r="AD15" s="23" t="s">
+      <c r="AD15" s="25" t="s">
         <v>446</v>
       </c>
-      <c r="AE15" s="29" t="s">
+      <c r="AE15" s="31" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A16" s="30" t="s">
+      <c r="A16" s="39" t="s">
         <v>448</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="40" t="s">
         <v>449</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="41" t="s">
         <v>450</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="58" t="s">
         <v>451</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="40" t="s">
         <v>452</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="F16" s="43" t="s">
         <v>453</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="44" t="s">
         <v>454</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="45" t="s">
         <v>455</v>
       </c>
-      <c r="I16" s="28" t="s">
+      <c r="I16" s="46" t="s">
         <v>456</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="41" t="s">
         <v>457</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="40" t="s">
         <v>458</v>
       </c>
-      <c r="L16" s="23" t="s">
+      <c r="L16" s="40" t="s">
         <v>459</v>
       </c>
-      <c r="M16" s="23" t="s">
+      <c r="M16" s="40" t="s">
         <v>460</v>
       </c>
-      <c r="N16" s="24" t="s">
+      <c r="N16" s="59" t="s">
         <v>461</v>
       </c>
-      <c r="O16" s="16" t="s">
+      <c r="O16" s="41" t="s">
         <v>462</v>
       </c>
-      <c r="P16" s="25" t="s">
+      <c r="P16" s="43" t="s">
         <v>463</v>
       </c>
-      <c r="Q16" s="25" t="s">
+      <c r="Q16" s="43" t="s">
         <v>464</v>
       </c>
-      <c r="R16" s="23" t="s">
+      <c r="R16" s="40" t="s">
         <v>465</v>
       </c>
-      <c r="S16" s="26" t="s">
+      <c r="S16" s="44" t="s">
         <v>466</v>
       </c>
-      <c r="T16" s="41" t="s">
+      <c r="T16" s="45" t="s">
         <v>467</v>
       </c>
-      <c r="U16" s="29" t="s">
+      <c r="U16" s="46" t="s">
         <v>468</v>
       </c>
-      <c r="V16" s="23" t="s">
+      <c r="V16" s="40" t="s">
         <v>469</v>
       </c>
-      <c r="W16" s="34" t="s">
+      <c r="W16" s="40" t="s">
         <v>470</v>
       </c>
-      <c r="X16" s="34" t="s">
+      <c r="X16" s="41" t="s">
         <v>471</v>
       </c>
-      <c r="Y16" s="36" t="s">
+      <c r="Y16" s="59" t="s">
         <v>472</v>
       </c>
-      <c r="Z16" s="34" t="s">
+      <c r="Z16" s="40" t="s">
         <v>473</v>
       </c>
-      <c r="AA16" s="37" t="s">
+      <c r="AA16" s="43" t="s">
         <v>474</v>
       </c>
-      <c r="AB16" s="28" t="s">
+      <c r="AB16" s="46" t="s">
         <v>475</v>
       </c>
-      <c r="AC16" s="34" t="s">
+      <c r="AC16" s="40" t="s">
         <v>476</v>
       </c>
-      <c r="AD16" s="23" t="s">
+      <c r="AD16" s="25" t="s">
         <v>477</v>
       </c>
-      <c r="AE16" s="29" t="s">
+      <c r="AE16" s="31" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="47" t="s">
         <v>479</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="25" t="s">
         <v>480</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="18" t="s">
         <v>481</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="50" t="s">
         <v>482</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="25" t="s">
         <v>483</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="27" t="s">
         <v>484</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="48" t="s">
         <v>485</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="31" t="s">
         <v>487</v>
       </c>
-      <c r="J17" s="16" t="s">
+      <c r="J17" s="18" t="s">
         <v>488</v>
       </c>
-      <c r="K17" s="23" t="s">
+      <c r="K17" s="40" t="s">
         <v>489</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="L17" s="40" t="s">
         <v>490</v>
       </c>
-      <c r="M17" s="23" t="s">
+      <c r="M17" s="40" t="s">
         <v>491</v>
       </c>
-      <c r="N17" s="24" t="s">
+      <c r="N17" s="59" t="s">
         <v>492</v>
       </c>
-      <c r="O17" s="16" t="s">
+      <c r="O17" s="41" t="s">
         <v>493</v>
       </c>
-      <c r="P17" s="25" t="s">
+      <c r="P17" s="43" t="s">
         <v>494</v>
       </c>
-      <c r="Q17" s="25" t="s">
+      <c r="Q17" s="43" t="s">
         <v>495</v>
       </c>
-      <c r="R17" s="23" t="s">
+      <c r="R17" s="40" t="s">
         <v>496</v>
       </c>
-      <c r="S17" s="26" t="s">
+      <c r="S17" s="44" t="s">
         <v>497</v>
       </c>
-      <c r="T17" s="27" t="s">
+      <c r="T17" s="45" t="s">
         <v>498</v>
       </c>
-      <c r="U17" s="29" t="s">
+      <c r="U17" s="31" t="s">
         <v>499</v>
       </c>
-      <c r="V17" s="23" t="s">
+      <c r="V17" s="25" t="s">
         <v>500</v>
       </c>
-      <c r="W17" s="23" t="s">
+      <c r="W17" s="25" t="s">
         <v>501</v>
       </c>
-      <c r="X17" s="16" t="s">
+      <c r="X17" s="18" t="s">
         <v>502</v>
       </c>
-      <c r="Y17" s="16">
+      <c r="Y17" s="18">
         <v>6015</v>
       </c>
-      <c r="Z17" s="23" t="s">
+      <c r="Z17" s="25" t="s">
         <v>503</v>
       </c>
-      <c r="AA17" s="25" t="s">
+      <c r="AA17" s="27" t="s">
         <v>504</v>
       </c>
-      <c r="AB17" s="29" t="s">
+      <c r="AB17" s="31" t="s">
         <v>505</v>
       </c>
-      <c r="AC17" s="23" t="s">
+      <c r="AC17" s="25" t="s">
         <v>506</v>
       </c>
-      <c r="AD17" s="23" t="s">
+      <c r="AD17" s="25" t="s">
         <v>507</v>
       </c>
-      <c r="AE17" s="29" t="s">
+      <c r="AE17" s="31" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="47" t="s">
         <v>509</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="25" t="s">
         <v>510</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="D18" s="16" t="s">
+      <c r="D18" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="25" t="s">
         <v>513</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="F18" s="27" t="s">
         <v>514</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="48" t="s">
         <v>515</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="49" t="s">
         <v>516</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="30" t="s">
         <v>517</v>
       </c>
-      <c r="J18" s="16" t="s">
+      <c r="J18" s="18" t="s">
         <v>518</v>
       </c>
-      <c r="K18" s="23" t="s">
+      <c r="K18" s="25" t="s">
         <v>519</v>
       </c>
-      <c r="L18" s="23" t="s">
+      <c r="L18" s="25" t="s">
         <v>520</v>
       </c>
-      <c r="M18" s="23" t="s">
+      <c r="M18" s="25" t="s">
         <v>521</v>
       </c>
-      <c r="N18" s="16" t="s">
+      <c r="N18" s="18" t="s">
         <v>522</v>
       </c>
-      <c r="O18" s="16" t="s">
+      <c r="O18" s="18" t="s">
         <v>523</v>
       </c>
-      <c r="P18" s="25" t="s">
+      <c r="P18" s="27" t="s">
         <v>524</v>
       </c>
-      <c r="Q18" s="25" t="s">
+      <c r="Q18" s="27" t="s">
         <v>525</v>
       </c>
-      <c r="R18" s="23" t="s">
+      <c r="R18" s="25" t="s">
         <v>526</v>
       </c>
-      <c r="S18" s="26" t="s">
+      <c r="S18" s="28" t="s">
         <v>527</v>
       </c>
-      <c r="T18" s="27" t="s">
+      <c r="T18" s="29" t="s">
         <v>528</v>
       </c>
-      <c r="U18" s="29" t="s">
+      <c r="U18" s="31" t="s">
         <v>529</v>
       </c>
-      <c r="V18" s="23" t="s">
+      <c r="V18" s="40" t="s">
         <v>530</v>
       </c>
-      <c r="W18" s="23" t="s">
+      <c r="W18" s="40" t="s">
         <v>531</v>
       </c>
-      <c r="X18" s="16" t="s">
+      <c r="X18" s="41" t="s">
         <v>532</v>
       </c>
-      <c r="Y18" s="24" t="s">
+      <c r="Y18" s="59" t="s">
         <v>533</v>
       </c>
-      <c r="Z18" s="23" t="s">
+      <c r="Z18" s="40" t="s">
         <v>534</v>
       </c>
-      <c r="AA18" s="25" t="s">
+      <c r="AA18" s="43" t="s">
         <v>535</v>
       </c>
-      <c r="AB18" s="29" t="s">
+      <c r="AB18" s="46" t="s">
         <v>536</v>
       </c>
-      <c r="AC18" s="23" t="s">
+      <c r="AC18" s="40" t="s">
         <v>537</v>
       </c>
-      <c r="AD18" s="23" t="s">
+      <c r="AD18" s="25" t="s">
         <v>538</v>
       </c>
-      <c r="AE18" s="29" t="s">
+      <c r="AE18" s="31" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="47" t="s">
         <v>540</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="25" t="s">
         <v>541</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="18" t="s">
         <v>542</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="18" t="s">
         <v>543</v>
       </c>
-      <c r="E19" s="23" t="s">
+      <c r="E19" s="25" t="s">
         <v>544</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="F19" s="27" t="s">
         <v>545</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="48" t="s">
         <v>546</v>
       </c>
-      <c r="H19" s="32" t="s">
+      <c r="H19" s="49" t="s">
         <v>547</v>
       </c>
-      <c r="I19" s="28" t="s">
+      <c r="I19" s="30" t="s">
         <v>548</v>
       </c>
-      <c r="J19" s="16" t="s">
+      <c r="J19" s="18" t="s">
         <v>549</v>
       </c>
-      <c r="K19" s="23" t="s">
+      <c r="K19" s="25" t="s">
         <v>550</v>
       </c>
-      <c r="L19" s="23" t="s">
+      <c r="L19" s="25" t="s">
         <v>551</v>
       </c>
-      <c r="M19" s="23" t="s">
+      <c r="M19" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="N19" s="16" t="s">
+      <c r="N19" s="18" t="s">
         <v>553</v>
       </c>
-      <c r="O19" s="16" t="s">
+      <c r="O19" s="18" t="s">
         <v>554</v>
       </c>
-      <c r="P19" s="25" t="s">
+      <c r="P19" s="27" t="s">
         <v>555</v>
       </c>
-      <c r="Q19" s="25" t="s">
+      <c r="Q19" s="27" t="s">
         <v>556</v>
       </c>
-      <c r="R19" s="23" t="s">
+      <c r="R19" s="25" t="s">
         <v>557</v>
       </c>
-      <c r="S19" s="26" t="s">
+      <c r="S19" s="28" t="s">
         <v>558</v>
       </c>
-      <c r="T19" s="27" t="s">
+      <c r="T19" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="U19" s="29" t="s">
+      <c r="U19" s="31" t="s">
         <v>560</v>
       </c>
-      <c r="V19" s="23" t="s">
+      <c r="V19" s="25" t="s">
         <v>561</v>
       </c>
-      <c r="W19" s="23" t="s">
+      <c r="W19" s="25" t="s">
         <v>562</v>
       </c>
-      <c r="X19" s="16" t="s">
+      <c r="X19" s="18" t="s">
         <v>563</v>
       </c>
-      <c r="Y19" s="16" t="s">
+      <c r="Y19" s="18" t="s">
         <v>564</v>
       </c>
-      <c r="Z19" s="23" t="s">
+      <c r="Z19" s="25" t="s">
         <v>565</v>
       </c>
-      <c r="AA19" s="25" t="s">
+      <c r="AA19" s="27" t="s">
         <v>566</v>
       </c>
-      <c r="AB19" s="29" t="s">
+      <c r="AB19" s="31" t="s">
         <v>567</v>
       </c>
-      <c r="AC19" s="23" t="s">
+      <c r="AC19" s="25" t="s">
         <v>568</v>
       </c>
-      <c r="AD19" s="23" t="s">
+      <c r="AD19" s="25" t="s">
         <v>569</v>
       </c>
-      <c r="AE19" s="29" t="s">
+      <c r="AE19" s="31" t="s">
         <v>570</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="47" t="s">
         <v>571</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="25" t="s">
         <v>572</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="18" t="s">
         <v>573</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="18" t="s">
         <v>574</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="F20" s="27" t="s">
         <v>576</v>
       </c>
-      <c r="G20" s="31" t="s">
+      <c r="G20" s="48" t="s">
         <v>577</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="49" t="s">
         <v>578</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="I20" s="30" t="s">
         <v>579</v>
       </c>
-      <c r="J20" s="16" t="s">
+      <c r="J20" s="18" t="s">
         <v>580</v>
       </c>
-      <c r="K20" s="23" t="s">
+      <c r="K20" s="40" t="s">
         <v>581</v>
       </c>
-      <c r="L20" s="23" t="s">
+      <c r="L20" s="40" t="s">
         <v>582</v>
       </c>
-      <c r="M20" s="23" t="s">
+      <c r="M20" s="40" t="s">
         <v>583</v>
       </c>
-      <c r="N20" s="24" t="s">
+      <c r="N20" s="59" t="s">
         <v>584</v>
       </c>
-      <c r="O20" s="16" t="s">
+      <c r="O20" s="41" t="s">
         <v>585</v>
       </c>
-      <c r="P20" s="25" t="s">
+      <c r="P20" s="43" t="s">
         <v>586</v>
       </c>
-      <c r="Q20" s="25" t="s">
+      <c r="Q20" s="43" t="s">
         <v>587</v>
       </c>
-      <c r="R20" s="23" t="s">
+      <c r="R20" s="40" t="s">
         <v>588</v>
       </c>
-      <c r="S20" s="26" t="s">
+      <c r="S20" s="44" t="s">
         <v>589</v>
       </c>
-      <c r="T20" s="27" t="s">
+      <c r="T20" s="45" t="s">
         <v>590</v>
       </c>
-      <c r="U20" s="29" t="s">
+      <c r="U20" s="31" t="s">
         <v>591</v>
       </c>
-      <c r="V20" s="23" t="s">
+      <c r="V20" s="25" t="s">
         <v>592</v>
       </c>
-      <c r="W20" s="23" t="s">
+      <c r="W20" s="25" t="s">
         <v>593</v>
       </c>
-      <c r="X20" s="16" t="s">
+      <c r="X20" s="18" t="s">
         <v>594</v>
       </c>
-      <c r="Y20" s="16">
+      <c r="Y20" s="18">
         <v>6605</v>
       </c>
-      <c r="Z20" s="23" t="s">
+      <c r="Z20" s="25" t="s">
         <v>595</v>
       </c>
-      <c r="AA20" s="25" t="s">
+      <c r="AA20" s="27" t="s">
         <v>596</v>
       </c>
-      <c r="AB20" s="29" t="s">
+      <c r="AB20" s="31" t="s">
         <v>597</v>
       </c>
-      <c r="AC20" s="23" t="s">
+      <c r="AC20" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="AD20" s="23" t="s">
+      <c r="AD20" s="25" t="s">
         <v>599</v>
       </c>
-      <c r="AE20" s="23" t="s">
+      <c r="AE20" s="25" t="s">
         <v>600</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="60" t="s">
         <v>601</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="61" t="s">
         <v>602</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="62" t="s">
         <v>603</v>
       </c>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="62" t="s">
         <v>604</v>
       </c>
-      <c r="E21" s="23" t="s">
+      <c r="E21" s="61" t="s">
         <v>605</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="63" t="s">
         <v>606</v>
       </c>
-      <c r="G21" s="26" t="s">
+      <c r="G21" s="64" t="s">
         <v>607</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="H21" s="65" t="s">
         <v>608</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I21" s="66" t="s">
         <v>609</v>
       </c>
-      <c r="J21" s="16" t="s">
+      <c r="J21" s="62" t="s">
         <v>610</v>
       </c>
-      <c r="K21" s="23" t="s">
+      <c r="K21" s="25" t="s">
         <v>611</v>
       </c>
-      <c r="L21" s="23" t="s">
+      <c r="L21" s="25" t="s">
         <v>612</v>
       </c>
-      <c r="M21" s="23" t="s">
+      <c r="M21" s="25" t="s">
         <v>613</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N21" s="18">
         <v>6874</v>
       </c>
-      <c r="O21" s="16" t="s">
+      <c r="O21" s="18" t="s">
         <v>614</v>
       </c>
-      <c r="P21" s="25" t="s">
+      <c r="P21" s="27" t="s">
         <v>615</v>
       </c>
-      <c r="Q21" s="25" t="s">
+      <c r="Q21" s="27" t="s">
         <v>616</v>
       </c>
-      <c r="R21" s="23" t="s">
+      <c r="R21" s="25" t="s">
         <v>617</v>
       </c>
-      <c r="S21" s="26" t="s">
+      <c r="S21" s="28" t="s">
         <v>618</v>
       </c>
-      <c r="T21" s="27" t="s">
+      <c r="T21" s="29" t="s">
         <v>619</v>
       </c>
-      <c r="U21" s="29" t="s">
+      <c r="U21" s="31" t="s">
         <v>620</v>
       </c>
-      <c r="V21" s="23" t="s">
+      <c r="V21" s="40" t="s">
         <v>621</v>
       </c>
-      <c r="W21" s="23" t="s">
+      <c r="W21" s="40" t="s">
         <v>622</v>
       </c>
-      <c r="X21" s="16" t="s">
+      <c r="X21" s="41" t="s">
         <v>623</v>
       </c>
-      <c r="Y21" s="16" t="s">
+      <c r="Y21" s="41" t="s">
         <v>624</v>
       </c>
-      <c r="Z21" s="23" t="s">
+      <c r="Z21" s="40" t="s">
         <v>625</v>
       </c>
-      <c r="AA21" s="25" t="s">
+      <c r="AA21" s="43" t="s">
         <v>626</v>
       </c>
-      <c r="AB21" s="29" t="s">
+      <c r="AB21" s="46" t="s">
         <v>627</v>
       </c>
-      <c r="AC21" s="23" t="s">
+      <c r="AC21" s="40" t="s">
         <v>628</v>
       </c>
-      <c r="AD21" s="23" t="s">
+      <c r="AD21" s="25" t="s">
         <v>629</v>
       </c>
-      <c r="AE21" s="23" t="s">
+      <c r="AE21" s="25" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="47" t="s">
         <v>631</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="25" t="s">
         <v>632</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="18" t="s">
         <v>633</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="50" t="s">
         <v>634</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="25" t="s">
         <v>635</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="27" t="s">
         <v>636</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="28" t="s">
         <v>637</v>
       </c>
-      <c r="H22" s="27" t="s">
+      <c r="H22" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="I22" s="28" t="s">
+      <c r="I22" s="30" t="s">
         <v>639</v>
       </c>
-      <c r="J22" s="16" t="s">
+      <c r="J22" s="18" t="s">
         <v>640</v>
       </c>
-      <c r="K22" s="23" t="s">
+      <c r="K22" s="25" t="s">
         <v>641</v>
       </c>
-      <c r="L22" s="23" t="s">
+      <c r="L22" s="25" t="s">
         <v>642</v>
       </c>
-      <c r="M22" s="23" t="s">
+      <c r="M22" s="25" t="s">
         <v>643</v>
       </c>
-      <c r="N22" s="24" t="s">
+      <c r="N22" s="26" t="s">
         <v>644</v>
       </c>
-      <c r="O22" s="16" t="s">
+      <c r="O22" s="18" t="s">
         <v>645</v>
       </c>
-      <c r="P22" s="25" t="s">
+      <c r="P22" s="27" t="s">
         <v>646</v>
       </c>
-      <c r="Q22" s="25" t="s">
+      <c r="Q22" s="27" t="s">
         <v>647</v>
       </c>
-      <c r="R22" s="23" t="s">
+      <c r="R22" s="25" t="s">
         <v>648</v>
       </c>
-      <c r="S22" s="26" t="s">
+      <c r="S22" s="28" t="s">
         <v>649</v>
       </c>
-      <c r="T22" s="27" t="s">
+      <c r="T22" s="29" t="s">
         <v>650</v>
       </c>
-      <c r="U22" s="29" t="s">
+      <c r="U22" s="31" t="s">
         <v>651</v>
       </c>
-      <c r="V22" s="23" t="s">
+      <c r="V22" s="25" t="s">
         <v>652</v>
       </c>
-      <c r="W22" s="23" t="s">
+      <c r="W22" s="25" t="s">
         <v>653</v>
       </c>
-      <c r="X22" s="16" t="s">
+      <c r="X22" s="18" t="s">
         <v>654</v>
       </c>
-      <c r="Y22" s="16" t="s">
+      <c r="Y22" s="18" t="s">
         <v>655</v>
       </c>
-      <c r="Z22" s="23" t="s">
+      <c r="Z22" s="25" t="s">
         <v>656</v>
       </c>
-      <c r="AA22" s="25" t="s">
+      <c r="AA22" s="27" t="s">
         <v>657</v>
       </c>
-      <c r="AB22" s="29" t="s">
+      <c r="AB22" s="31" t="s">
         <v>658</v>
       </c>
-      <c r="AC22" s="23" t="s">
+      <c r="AC22" s="25" t="s">
         <v>659</v>
       </c>
-      <c r="AD22" s="23" t="s">
+      <c r="AD22" s="25" t="s">
         <v>660</v>
       </c>
-      <c r="AE22" s="23" t="s">
+      <c r="AE22" s="25" t="s">
         <v>661</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="47" t="s">
         <v>662</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="25" t="s">
         <v>663</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="18" t="s">
         <v>664</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="50" t="s">
         <v>665</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="27" t="s">
         <v>667</v>
       </c>
-      <c r="G23" s="26" t="s">
+      <c r="G23" s="28" t="s">
         <v>668</v>
       </c>
-      <c r="H23" s="27" t="s">
+      <c r="H23" s="29" t="s">
         <v>669</v>
       </c>
-      <c r="I23" s="28" t="s">
+      <c r="I23" s="30" t="s">
         <v>670</v>
       </c>
-      <c r="J23" s="16" t="s">
+      <c r="J23" s="18" t="s">
         <v>671</v>
       </c>
-      <c r="K23" s="23" t="s">
+      <c r="K23" s="25" t="s">
         <v>672</v>
       </c>
-      <c r="L23" s="23" t="s">
+      <c r="L23" s="25" t="s">
         <v>673</v>
       </c>
-      <c r="M23" s="23" t="s">
+      <c r="M23" s="25" t="s">
         <v>674</v>
       </c>
-      <c r="N23" s="16" t="s">
+      <c r="N23" s="18" t="s">
         <v>675</v>
       </c>
-      <c r="O23" s="16" t="s">
+      <c r="O23" s="18" t="s">
         <v>676</v>
       </c>
-      <c r="P23" s="25" t="s">
+      <c r="P23" s="27" t="s">
         <v>677</v>
       </c>
-      <c r="Q23" s="25" t="s">
+      <c r="Q23" s="27" t="s">
         <v>678</v>
       </c>
-      <c r="R23" s="23" t="s">
+      <c r="R23" s="25" t="s">
         <v>679</v>
       </c>
-      <c r="S23" s="26" t="s">
+      <c r="S23" s="28" t="s">
         <v>680</v>
       </c>
-      <c r="T23" s="27" t="s">
+      <c r="T23" s="29" t="s">
         <v>681</v>
       </c>
-      <c r="U23" s="29" t="s">
+      <c r="U23" s="31" t="s">
         <v>682</v>
       </c>
-      <c r="V23" s="23" t="s">
+      <c r="V23" s="25" t="s">
         <v>683</v>
       </c>
-      <c r="W23" s="23" t="s">
+      <c r="W23" s="25" t="s">
         <v>684</v>
       </c>
-      <c r="X23" s="16" t="s">
+      <c r="X23" s="18" t="s">
         <v>685</v>
       </c>
-      <c r="Y23" s="16" t="s">
+      <c r="Y23" s="18" t="s">
         <v>686</v>
       </c>
-      <c r="Z23" s="23" t="s">
+      <c r="Z23" s="25" t="s">
         <v>687</v>
       </c>
-      <c r="AA23" s="25" t="s">
+      <c r="AA23" s="27" t="s">
         <v>688</v>
       </c>
-      <c r="AB23" s="29" t="s">
+      <c r="AB23" s="31" t="s">
         <v>689</v>
       </c>
-      <c r="AC23" s="23" t="s">
+      <c r="AC23" s="25" t="s">
         <v>690</v>
       </c>
-      <c r="AD23" s="23" t="s">
+      <c r="AD23" s="25" t="s">
         <v>691</v>
       </c>
-      <c r="AE23" s="23" t="s">
+      <c r="AE23" s="25" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="32" t="s">
         <v>693</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="33" t="s">
         <v>694</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="34" t="s">
         <v>695</v>
       </c>
-      <c r="D24" s="24" t="s">
+      <c r="D24" s="34" t="s">
         <v>696</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="33" t="s">
         <v>697</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="35" t="s">
         <v>698</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="36" t="s">
         <v>699</v>
       </c>
-      <c r="H24" s="32" t="s">
+      <c r="H24" s="37" t="s">
         <v>700</v>
       </c>
-      <c r="I24" s="28" t="s">
+      <c r="I24" s="38" t="s">
         <v>701</v>
       </c>
-      <c r="J24" s="16" t="s">
+      <c r="J24" s="34" t="s">
         <v>702</v>
       </c>
-      <c r="K24" s="23" t="s">
+      <c r="K24" s="40" t="s">
         <v>703</v>
       </c>
-      <c r="L24" s="23" t="s">
+      <c r="L24" s="40" t="s">
         <v>704</v>
       </c>
-      <c r="M24" s="23" t="s">
+      <c r="M24" s="40" t="s">
         <v>705</v>
       </c>
-      <c r="N24" s="16">
+      <c r="N24" s="41">
         <v>6674</v>
       </c>
-      <c r="O24" s="16" t="s">
+      <c r="O24" s="41" t="s">
         <v>706</v>
       </c>
-      <c r="P24" s="25" t="s">
+      <c r="P24" s="43" t="s">
         <v>707</v>
       </c>
-      <c r="Q24" s="25" t="s">
+      <c r="Q24" s="43" t="s">
         <v>708</v>
       </c>
-      <c r="R24" s="23" t="s">
+      <c r="R24" s="40" t="s">
         <v>709</v>
       </c>
-      <c r="S24" s="26" t="s">
+      <c r="S24" s="44" t="s">
         <v>710</v>
       </c>
-      <c r="T24" s="27" t="s">
+      <c r="T24" s="45" t="s">
         <v>711</v>
       </c>
-      <c r="U24" s="29" t="s">
+      <c r="U24" s="31" t="s">
         <v>712</v>
       </c>
-      <c r="V24" s="23" t="s">
+      <c r="V24" s="25" t="s">
         <v>713</v>
       </c>
-      <c r="W24" s="23" t="s">
+      <c r="W24" s="25" t="s">
         <v>714</v>
       </c>
-      <c r="X24" s="16" t="s">
+      <c r="X24" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="Y24" s="16" t="s">
+      <c r="Y24" s="18" t="s">
         <v>716</v>
       </c>
-      <c r="Z24" s="23" t="s">
+      <c r="Z24" s="25" t="s">
         <v>717</v>
       </c>
-      <c r="AA24" s="25" t="s">
+      <c r="AA24" s="27" t="s">
         <v>718</v>
       </c>
-      <c r="AB24" s="29" t="s">
+      <c r="AB24" s="31" t="s">
         <v>719</v>
       </c>
-      <c r="AC24" s="23" t="s">
+      <c r="AC24" s="25" t="s">
         <v>720</v>
       </c>
-      <c r="AD24" s="23" t="s">
+      <c r="AD24" s="25" t="s">
         <v>721</v>
       </c>
-      <c r="AE24" s="23" t="s">
+      <c r="AE24" s="25" t="s">
         <v>722</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="47" t="s">
         <v>723</v>
       </c>
-      <c r="B25" s="23" t="s">
+      <c r="B25" s="25" t="s">
         <v>724</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="18" t="s">
         <v>725</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="18" t="s">
         <v>726</v>
       </c>
-      <c r="E25" s="23" t="s">
+      <c r="E25" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="27" t="s">
         <v>728</v>
       </c>
-      <c r="G25" s="26" t="s">
+      <c r="G25" s="28" t="s">
         <v>729</v>
       </c>
-      <c r="H25" s="27" t="s">
+      <c r="H25" s="29" t="s">
         <v>730</v>
       </c>
-      <c r="I25" s="28" t="s">
+      <c r="I25" s="30" t="s">
         <v>731</v>
       </c>
-      <c r="J25" s="16" t="s">
+      <c r="J25" s="18" t="s">
         <v>732</v>
       </c>
-      <c r="K25" s="23" t="s">
+      <c r="K25" s="18" t="s">
         <v>733</v>
       </c>
-      <c r="L25" s="23" t="s">
+      <c r="L25" s="25" t="s">
         <v>734</v>
       </c>
-      <c r="M25" s="23" t="s">
+      <c r="M25" s="25" t="s">
         <v>735</v>
       </c>
-      <c r="N25" s="16">
+      <c r="N25" s="18">
         <v>6078</v>
       </c>
-      <c r="O25" s="16" t="s">
+      <c r="O25" s="18" t="s">
         <v>736</v>
       </c>
-      <c r="P25" s="25" t="s">
+      <c r="P25" s="27" t="s">
         <v>737</v>
       </c>
-      <c r="Q25" s="25" t="s">
+      <c r="Q25" s="27" t="s">
         <v>738</v>
       </c>
-      <c r="R25" s="23" t="s">
+      <c r="R25" s="25" t="s">
         <v>739</v>
       </c>
-      <c r="S25" s="26" t="s">
+      <c r="S25" s="28" t="s">
         <v>740</v>
       </c>
-      <c r="T25" s="27" t="s">
+      <c r="T25" s="29" t="s">
         <v>741</v>
       </c>
-      <c r="U25" s="29" t="s">
+      <c r="U25" s="31" t="s">
         <v>742</v>
       </c>
-      <c r="V25" s="23" t="s">
+      <c r="V25" s="40" t="s">
         <v>743</v>
       </c>
-      <c r="W25" s="23" t="s">
+      <c r="W25" s="40" t="s">
         <v>744</v>
       </c>
-      <c r="X25" s="16" t="s">
+      <c r="X25" s="41" t="s">
         <v>745</v>
       </c>
-      <c r="Y25" s="16" t="s">
+      <c r="Y25" s="41" t="s">
         <v>746</v>
       </c>
-      <c r="Z25" s="23" t="s">
+      <c r="Z25" s="40" t="s">
         <v>747</v>
       </c>
-      <c r="AA25" s="25" t="s">
+      <c r="AA25" s="43" t="s">
         <v>748</v>
       </c>
-      <c r="AB25" s="29" t="s">
+      <c r="AB25" s="46" t="s">
         <v>749</v>
       </c>
-      <c r="AC25" s="23" t="s">
+      <c r="AC25" s="40" t="s">
         <v>750</v>
       </c>
-      <c r="AD25" s="23" t="s">
+      <c r="AD25" s="25" t="s">
         <v>751</v>
       </c>
-      <c r="AE25" s="23" t="s">
+      <c r="AE25" s="25" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="47" t="s">
         <v>753</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="25" t="s">
         <v>754</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="18" t="s">
         <v>755</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="50" t="s">
         <v>756</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="25" t="s">
         <v>757</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="F26" s="27" t="s">
         <v>758</v>
       </c>
-      <c r="G26" s="26" t="s">
+      <c r="G26" s="28" t="s">
         <v>759</v>
       </c>
-      <c r="H26" s="27" t="s">
+      <c r="H26" s="29" t="s">
         <v>760</v>
       </c>
-      <c r="I26" s="28" t="s">
+      <c r="I26" s="30" t="s">
         <v>761</v>
       </c>
-      <c r="J26" s="16" t="s">
+      <c r="J26" s="18" t="s">
         <v>762</v>
       </c>
-      <c r="K26" s="23" t="s">
+      <c r="K26" s="25" t="s">
         <v>763</v>
       </c>
-      <c r="L26" s="23" t="s">
+      <c r="L26" s="25" t="s">
         <v>764</v>
       </c>
-      <c r="M26" s="23" t="s">
+      <c r="M26" s="25" t="s">
         <v>765</v>
       </c>
-      <c r="N26" s="16" t="s">
+      <c r="N26" s="18" t="s">
         <v>766</v>
       </c>
-      <c r="O26" s="16" t="s">
+      <c r="O26" s="18" t="s">
         <v>767</v>
       </c>
-      <c r="P26" s="25" t="s">
+      <c r="P26" s="27" t="s">
         <v>768</v>
       </c>
-      <c r="Q26" s="25" t="s">
+      <c r="Q26" s="27" t="s">
         <v>769</v>
       </c>
-      <c r="R26" s="23" t="s">
+      <c r="R26" s="25" t="s">
         <v>770</v>
       </c>
-      <c r="S26" s="26" t="s">
+      <c r="S26" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="T26" s="27" t="s">
+      <c r="T26" s="29" t="s">
         <v>772</v>
       </c>
-      <c r="U26" s="29" t="s">
+      <c r="U26" s="31" t="s">
         <v>773</v>
       </c>
-      <c r="V26" s="23" t="s">
+      <c r="V26" s="25" t="s">
         <v>774</v>
       </c>
-      <c r="W26" s="23" t="s">
+      <c r="W26" s="25" t="s">
         <v>775</v>
       </c>
-      <c r="X26" s="16" t="s">
+      <c r="X26" s="18" t="s">
         <v>776</v>
       </c>
-      <c r="Y26" s="16" t="s">
+      <c r="Y26" s="18" t="s">
         <v>777</v>
       </c>
-      <c r="Z26" s="23" t="s">
+      <c r="Z26" s="25" t="s">
         <v>778</v>
       </c>
-      <c r="AA26" s="25" t="s">
+      <c r="AA26" s="27" t="s">
         <v>779</v>
       </c>
-      <c r="AB26" s="29" t="s">
+      <c r="AB26" s="31" t="s">
         <v>780</v>
       </c>
-      <c r="AC26" s="23" t="s">
+      <c r="AC26" s="25" t="s">
         <v>781</v>
       </c>
-      <c r="AD26" s="23" t="s">
+      <c r="AD26" s="25" t="s">
         <v>782</v>
       </c>
-      <c r="AE26" s="23" t="s">
+      <c r="AE26" s="25" t="s">
         <v>783</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="47" t="s">
         <v>784</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="25" t="s">
         <v>785</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="18" t="s">
         <v>786</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="18" t="s">
         <v>787</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="25" t="s">
         <v>788</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="27" t="s">
         <v>789</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="48" t="s">
         <v>790</v>
       </c>
-      <c r="H27" s="32" t="s">
+      <c r="H27" s="49" t="s">
         <v>791</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="30" t="s">
         <v>792</v>
       </c>
-      <c r="J27" s="16" t="s">
+      <c r="J27" s="18" t="s">
         <v>793</v>
       </c>
-      <c r="K27" s="23" t="s">
+      <c r="K27" s="25" t="s">
         <v>794</v>
       </c>
-      <c r="L27" s="23" t="s">
+      <c r="L27" s="25" t="s">
         <v>795</v>
       </c>
-      <c r="M27" s="23" t="s">
+      <c r="M27" s="25" t="s">
         <v>796</v>
       </c>
-      <c r="N27" s="16" t="s">
+      <c r="N27" s="18" t="s">
         <v>797</v>
       </c>
-      <c r="O27" s="16" t="s">
+      <c r="O27" s="18" t="s">
         <v>798</v>
       </c>
-      <c r="P27" s="25" t="s">
+      <c r="P27" s="27" t="s">
         <v>799</v>
       </c>
-      <c r="Q27" s="25" t="s">
+      <c r="Q27" s="27" t="s">
         <v>800</v>
       </c>
-      <c r="R27" s="23" t="s">
+      <c r="R27" s="25" t="s">
         <v>801</v>
       </c>
-      <c r="S27" s="26" t="s">
+      <c r="S27" s="28" t="s">
         <v>802</v>
       </c>
-      <c r="T27" s="27" t="s">
+      <c r="T27" s="29" t="s">
         <v>803</v>
       </c>
-      <c r="U27" s="29" t="s">
+      <c r="U27" s="31" t="s">
         <v>804</v>
       </c>
-      <c r="V27" s="23" t="s">
+      <c r="V27" s="25" t="s">
         <v>805</v>
       </c>
-      <c r="W27" s="23" t="s">
+      <c r="W27" s="25" t="s">
         <v>806</v>
       </c>
-      <c r="X27" s="16" t="s">
+      <c r="X27" s="18" t="s">
         <v>807</v>
       </c>
-      <c r="Y27" s="16" t="s">
+      <c r="Y27" s="18" t="s">
         <v>808</v>
       </c>
-      <c r="Z27" s="23" t="s">
+      <c r="Z27" s="25" t="s">
         <v>809</v>
       </c>
-      <c r="AA27" s="25" t="s">
+      <c r="AA27" s="27" t="s">
         <v>810</v>
       </c>
-      <c r="AB27" s="29" t="s">
+      <c r="AB27" s="31" t="s">
         <v>811</v>
       </c>
-      <c r="AC27" s="23" t="s">
+      <c r="AC27" s="25" t="s">
         <v>812</v>
       </c>
-      <c r="AD27" s="23" t="s">
+      <c r="AD27" s="25" t="s">
         <v>813</v>
       </c>
-      <c r="AE27" s="23" t="s">
+      <c r="AE27" s="25" t="s">
         <v>814</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="39" t="s">
         <v>815</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="40" t="s">
         <v>816</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="41" t="s">
         <v>817</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="58" t="s">
         <v>818</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="40" t="s">
         <v>819</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F28" s="43" t="s">
         <v>820</v>
       </c>
-      <c r="G28" s="26" t="s">
+      <c r="G28" s="44" t="s">
         <v>821</v>
       </c>
-      <c r="H28" s="27" t="s">
+      <c r="H28" s="45" t="s">
         <v>822</v>
       </c>
-      <c r="I28" s="28" t="s">
+      <c r="I28" s="67" t="s">
         <v>823</v>
       </c>
-      <c r="J28" s="16" t="s">
+      <c r="J28" s="41" t="s">
         <v>824</v>
       </c>
-      <c r="K28" s="23" t="s">
+      <c r="K28" s="40" t="s">
         <v>825</v>
       </c>
-      <c r="L28" s="23" t="s">
+      <c r="L28" s="40" t="s">
         <v>826</v>
       </c>
-      <c r="M28" s="23" t="s">
+      <c r="M28" s="40" t="s">
         <v>827</v>
       </c>
-      <c r="N28" s="16" t="s">
+      <c r="N28" s="41">
+        <v>7734</v>
+      </c>
+      <c r="O28" s="41" t="s">
         <v>828</v>
       </c>
-      <c r="O28" s="16" t="s">
+      <c r="P28" s="43" t="s">
         <v>829</v>
       </c>
-      <c r="P28" s="25" t="s">
+      <c r="Q28" s="43" t="s">
         <v>830</v>
       </c>
-      <c r="Q28" s="25" t="s">
+      <c r="R28" s="40" t="s">
         <v>831</v>
       </c>
-      <c r="R28" s="23" t="s">
+      <c r="S28" s="44" t="s">
         <v>832</v>
       </c>
-      <c r="S28" s="26" t="s">
+      <c r="T28" s="45" t="s">
         <v>833</v>
       </c>
-      <c r="T28" s="27" t="s">
+      <c r="U28" s="31" t="s">
         <v>834</v>
       </c>
-      <c r="U28" s="29" t="s">
+      <c r="V28" s="25" t="s">
         <v>835</v>
       </c>
-      <c r="V28" s="23" t="s">
+      <c r="W28" s="25" t="s">
         <v>836</v>
       </c>
-      <c r="W28" s="23" t="s">
+      <c r="X28" s="18" t="s">
         <v>837</v>
       </c>
-      <c r="X28" s="16" t="s">
+      <c r="Y28" s="26" t="s">
         <v>838</v>
       </c>
-      <c r="Y28" s="24" t="s">
+      <c r="Z28" s="25" t="s">
         <v>839</v>
       </c>
-      <c r="Z28" s="23" t="s">
+      <c r="AA28" s="27" t="s">
         <v>840</v>
       </c>
-      <c r="AA28" s="25" t="s">
+      <c r="AB28" s="31" t="s">
         <v>841</v>
       </c>
-      <c r="AB28" s="29" t="s">
+      <c r="AC28" s="25" t="s">
         <v>842</v>
       </c>
-      <c r="AC28" s="23" t="s">
+      <c r="AD28" s="25" t="s">
         <v>843</v>
       </c>
-      <c r="AD28" s="23" t="s">
+      <c r="AE28" s="25" t="s">
         <v>844</v>
-      </c>
-      <c r="AE28" s="23" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A29" s="30" t="s">
+      <c r="A29" s="39" t="s">
+        <v>845</v>
+      </c>
+      <c r="B29" s="40" t="s">
         <v>846</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="C29" s="41" t="s">
         <v>847</v>
       </c>
-      <c r="C29" s="16" t="s">
+      <c r="D29" s="58" t="s">
         <v>848</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="E29" s="40" t="s">
         <v>849</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="F29" s="43" t="s">
         <v>850</v>
       </c>
-      <c r="F29" s="25" t="s">
+      <c r="G29" s="44" t="s">
         <v>851</v>
       </c>
-      <c r="G29" s="31" t="s">
+      <c r="H29" s="45" t="s">
         <v>852</v>
       </c>
-      <c r="H29" s="32" t="s">
+      <c r="I29" s="46" t="s">
         <v>853</v>
       </c>
-      <c r="I29" s="28" t="s">
+      <c r="J29" s="41" t="s">
         <v>854</v>
       </c>
-      <c r="J29" s="16" t="s">
+      <c r="K29" s="25" t="s">
         <v>855</v>
       </c>
-      <c r="K29" s="23" t="s">
+      <c r="L29" s="25" t="s">
         <v>856</v>
       </c>
-      <c r="L29" s="23" t="s">
+      <c r="M29" s="25" t="s">
         <v>857</v>
       </c>
-      <c r="M29" s="23" t="s">
+      <c r="N29" s="18" t="s">
         <v>858</v>
       </c>
-      <c r="N29" s="16" t="s">
+      <c r="O29" s="18" t="s">
         <v>859</v>
       </c>
-      <c r="O29" s="16" t="s">
+      <c r="P29" s="27" t="s">
         <v>860</v>
       </c>
-      <c r="P29" s="25" t="s">
+      <c r="Q29" s="27" t="s">
         <v>861</v>
       </c>
-      <c r="Q29" s="25" t="s">
+      <c r="R29" s="25" t="s">
         <v>862</v>
       </c>
-      <c r="R29" s="23" t="s">
+      <c r="S29" s="28" t="s">
         <v>863</v>
       </c>
-      <c r="S29" s="26" t="s">
+      <c r="T29" s="29" t="s">
         <v>864</v>
       </c>
-      <c r="T29" s="27" t="s">
+      <c r="U29" s="31" t="s">
         <v>865</v>
       </c>
-      <c r="U29" s="29" t="s">
+      <c r="V29" s="40" t="s">
         <v>866</v>
       </c>
-      <c r="V29" s="23" t="s">
+      <c r="W29" s="40" t="s">
         <v>867</v>
       </c>
-      <c r="W29" s="23" t="s">
+      <c r="X29" s="41" t="s">
         <v>868</v>
       </c>
-      <c r="X29" s="16" t="s">
+      <c r="Y29" s="59" t="s">
         <v>869</v>
       </c>
-      <c r="Y29" s="24" t="s">
+      <c r="Z29" s="40" t="s">
         <v>870</v>
       </c>
-      <c r="Z29" s="23" t="s">
+      <c r="AA29" s="43" t="s">
         <v>871</v>
       </c>
-      <c r="AA29" s="25" t="s">
+      <c r="AB29" s="46" t="s">
         <v>872</v>
       </c>
-      <c r="AB29" s="29" t="s">
+      <c r="AC29" s="40" t="s">
         <v>873</v>
       </c>
-      <c r="AC29" s="23" t="s">
+      <c r="AD29" s="25" t="s">
         <v>874</v>
       </c>
-      <c r="AD29" s="23" t="s">
+      <c r="AE29" s="25" t="s">
         <v>875</v>
-      </c>
-      <c r="AE29" s="23" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="47" t="s">
+        <v>876</v>
+      </c>
+      <c r="B30" s="25" t="s">
         <v>877</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="C30" s="18" t="s">
         <v>878</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="D30" s="18" t="s">
         <v>879</v>
       </c>
-      <c r="D30" s="16" t="s">
+      <c r="E30" s="25" t="s">
         <v>880</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="F30" s="27" t="s">
         <v>881</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="G30" s="48" t="s">
         <v>882</v>
       </c>
-      <c r="G30" s="31" t="s">
+      <c r="H30" s="49" t="s">
         <v>883</v>
       </c>
-      <c r="H30" s="32" t="s">
+      <c r="I30" s="30" t="s">
         <v>884</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="J30" s="18" t="s">
         <v>885</v>
       </c>
-      <c r="J30" s="16" t="s">
+      <c r="K30" s="25" t="s">
         <v>886</v>
       </c>
-      <c r="K30" s="23" t="s">
+      <c r="L30" s="25" t="s">
         <v>887</v>
       </c>
-      <c r="L30" s="23" t="s">
+      <c r="M30" s="25" t="s">
         <v>888</v>
       </c>
-      <c r="M30" s="23" t="s">
+      <c r="N30" s="26" t="s">
         <v>889</v>
       </c>
-      <c r="N30" s="24" t="s">
+      <c r="O30" s="18" t="s">
         <v>890</v>
       </c>
-      <c r="O30" s="16" t="s">
+      <c r="P30" s="27" t="s">
         <v>891</v>
       </c>
-      <c r="P30" s="25" t="s">
+      <c r="Q30" s="27" t="s">
         <v>892</v>
       </c>
-      <c r="Q30" s="25" t="s">
+      <c r="R30" s="25" t="s">
         <v>893</v>
       </c>
-      <c r="R30" s="23" t="s">
+      <c r="S30" s="28" t="s">
         <v>894</v>
       </c>
-      <c r="S30" s="26" t="s">
+      <c r="T30" s="29" t="s">
         <v>895</v>
       </c>
-      <c r="T30" s="27" t="s">
+      <c r="U30" s="31" t="s">
         <v>896</v>
       </c>
-      <c r="U30" s="29" t="s">
+      <c r="V30" s="25" t="s">
         <v>897</v>
       </c>
-      <c r="V30" s="23" t="s">
+      <c r="W30" s="25" t="s">
         <v>898</v>
       </c>
-      <c r="W30" s="23" t="s">
+      <c r="X30" s="18" t="s">
         <v>899</v>
       </c>
-      <c r="X30" s="16" t="s">
+      <c r="Y30" s="18" t="s">
         <v>900</v>
       </c>
-      <c r="Y30" s="16" t="s">
+      <c r="Z30" s="25" t="s">
         <v>901</v>
       </c>
-      <c r="Z30" s="23" t="s">
+      <c r="AA30" s="27" t="s">
         <v>902</v>
       </c>
-      <c r="AA30" s="25" t="s">
+      <c r="AB30" s="31" t="s">
         <v>903</v>
       </c>
-      <c r="AB30" s="29" t="s">
+      <c r="AC30" s="25" t="s">
         <v>904</v>
       </c>
-      <c r="AC30" s="23" t="s">
+      <c r="AD30" s="25" t="s">
         <v>905</v>
       </c>
-      <c r="AD30" s="23" t="s">
+      <c r="AE30" s="25" t="s">
         <v>906</v>
-      </c>
-      <c r="AE30" s="23" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="39" t="s">
+        <v>907</v>
+      </c>
+      <c r="B31" s="40" t="s">
         <v>908</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="C31" s="41" t="s">
         <v>909</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="D31" s="41" t="s">
         <v>910</v>
       </c>
-      <c r="D31" s="16" t="s">
+      <c r="E31" s="40" t="s">
         <v>911</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="43" t="s">
         <v>912</v>
       </c>
-      <c r="F31" s="25" t="s">
+      <c r="G31" s="44" t="s">
         <v>913</v>
       </c>
-      <c r="G31" s="26" t="s">
+      <c r="H31" s="45" t="s">
         <v>914</v>
       </c>
-      <c r="H31" s="27" t="s">
+      <c r="I31" s="67" t="s">
         <v>915</v>
       </c>
-      <c r="I31" s="28" t="s">
+      <c r="J31" s="41" t="s">
         <v>916</v>
       </c>
-      <c r="J31" s="16" t="s">
+      <c r="K31" s="25" t="s">
         <v>917</v>
       </c>
-      <c r="K31" s="23" t="s">
+      <c r="L31" s="25" t="s">
         <v>918</v>
       </c>
-      <c r="L31" s="23" t="s">
+      <c r="M31" s="25" t="s">
         <v>919</v>
       </c>
-      <c r="M31" s="23" t="s">
+      <c r="N31" s="18">
+        <v>6074</v>
+      </c>
+      <c r="O31" s="18" t="s">
         <v>920</v>
       </c>
-      <c r="N31" s="16">
-        <v>6074</v>
-      </c>
-      <c r="O31" s="16" t="s">
+      <c r="P31" s="27" t="s">
         <v>921</v>
       </c>
-      <c r="P31" s="25" t="s">
+      <c r="Q31" s="27" t="s">
         <v>922</v>
       </c>
-      <c r="Q31" s="25" t="s">
+      <c r="R31" s="25" t="s">
         <v>923</v>
       </c>
-      <c r="R31" s="23" t="s">
+      <c r="S31" s="28" t="s">
         <v>924</v>
       </c>
-      <c r="S31" s="26" t="s">
+      <c r="T31" s="29" t="s">
         <v>925</v>
       </c>
-      <c r="T31" s="27" t="s">
+      <c r="U31" s="31" t="s">
         <v>926</v>
       </c>
-      <c r="U31" s="29" t="s">
+      <c r="V31" s="25" t="s">
         <v>927</v>
       </c>
-      <c r="V31" s="23" t="s">
+      <c r="W31" s="25" t="s">
         <v>928</v>
       </c>
-      <c r="W31" s="23" t="s">
+      <c r="X31" s="18" t="s">
         <v>929</v>
       </c>
-      <c r="X31" s="16" t="s">
+      <c r="Y31" s="18" t="s">
         <v>930</v>
       </c>
-      <c r="Y31" s="16" t="s">
+      <c r="Z31" s="25" t="s">
         <v>931</v>
       </c>
-      <c r="Z31" s="23" t="s">
+      <c r="AA31" s="27" t="s">
         <v>932</v>
       </c>
-      <c r="AA31" s="25" t="s">
+      <c r="AB31" s="31" t="s">
         <v>933</v>
       </c>
-      <c r="AB31" s="29" t="s">
+      <c r="AC31" s="25" t="s">
         <v>934</v>
       </c>
-      <c r="AC31" s="23" t="s">
+      <c r="AD31" s="25" t="s">
         <v>935</v>
       </c>
-      <c r="AD31" s="23" t="s">
+      <c r="AE31" s="25" t="s">
         <v>936</v>
-      </c>
-      <c r="AE31" s="23" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A32" s="30" t="s">
+      <c r="A32" s="32" t="s">
+        <v>937</v>
+      </c>
+      <c r="B32" s="33" t="s">
         <v>938</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="C32" s="34" t="s">
         <v>939</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="D32" s="68" t="s">
         <v>940</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="E32" s="33" t="s">
         <v>941</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="F32" s="35" t="s">
         <v>942</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="G32" s="36" t="s">
         <v>943</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="H32" s="37" t="s">
         <v>944</v>
       </c>
-      <c r="H32" s="32" t="s">
+      <c r="I32" s="38" t="s">
         <v>945</v>
       </c>
-      <c r="I32" s="28" t="s">
+      <c r="J32" s="34" t="s">
         <v>946</v>
       </c>
-      <c r="J32" s="16" t="s">
+      <c r="K32" s="25" t="s">
         <v>947</v>
       </c>
-      <c r="K32" s="23" t="s">
+      <c r="L32" s="51" t="s">
         <v>948</v>
       </c>
-      <c r="L32" s="34" t="s">
+      <c r="M32" s="52" t="s">
         <v>949</v>
       </c>
-      <c r="M32" s="35" t="s">
+      <c r="N32" s="56" t="s">
         <v>950</v>
       </c>
-      <c r="N32" s="36" t="s">
+      <c r="O32" s="52" t="s">
         <v>951</v>
       </c>
-      <c r="O32" s="35" t="s">
+      <c r="P32" s="53" t="s">
         <v>952</v>
       </c>
-      <c r="P32" s="37" t="s">
+      <c r="Q32" s="53" t="s">
         <v>953</v>
       </c>
-      <c r="Q32" s="37" t="s">
+      <c r="R32" s="51" t="s">
         <v>954</v>
       </c>
-      <c r="R32" s="34" t="s">
+      <c r="S32" s="54" t="s">
         <v>955</v>
       </c>
-      <c r="S32" s="38" t="s">
+      <c r="T32" s="55" t="s">
         <v>956</v>
       </c>
-      <c r="T32" s="39" t="s">
+      <c r="U32" s="31" t="s">
         <v>957</v>
       </c>
-      <c r="U32" s="29" t="s">
+      <c r="V32" s="40" t="s">
         <v>958</v>
       </c>
-      <c r="V32" s="23" t="s">
+      <c r="W32" s="40" t="s">
         <v>959</v>
       </c>
-      <c r="W32" s="23" t="s">
+      <c r="X32" s="41" t="s">
         <v>960</v>
       </c>
-      <c r="X32" s="16" t="s">
+      <c r="Y32" s="59" t="s">
         <v>961</v>
       </c>
-      <c r="Y32" s="24" t="s">
+      <c r="Z32" s="40" t="s">
         <v>962</v>
       </c>
-      <c r="Z32" s="23" t="s">
+      <c r="AA32" s="43" t="s">
         <v>963</v>
       </c>
-      <c r="AA32" s="25" t="s">
+      <c r="AB32" s="46" t="s">
         <v>964</v>
       </c>
-      <c r="AB32" s="29" t="s">
+      <c r="AC32" s="40" t="s">
         <v>965</v>
       </c>
-      <c r="AC32" s="23" t="s">
+      <c r="AD32" s="57" t="s">
         <v>966</v>
       </c>
-      <c r="AD32" s="40" t="s">
+      <c r="AE32" s="57" t="s">
         <v>967</v>
-      </c>
-      <c r="AE32" s="40" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
+        <v>968</v>
+      </c>
+      <c r="B33" s="33" t="s">
         <v>969</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="C33" s="34" t="s">
         <v>970</v>
       </c>
-      <c r="C33" s="16" t="s">
+      <c r="D33" s="69" t="s">
         <v>971</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="E33" s="33" t="s">
         <v>972</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="F33" s="35" t="s">
         <v>973</v>
       </c>
-      <c r="F33" s="25" t="s">
+      <c r="G33" s="36" t="s">
         <v>974</v>
       </c>
-      <c r="G33" s="31" t="s">
+      <c r="H33" s="37" t="s">
         <v>975</v>
       </c>
-      <c r="H33" s="32" t="s">
+      <c r="I33" s="38" t="s">
         <v>976</v>
       </c>
-      <c r="I33" s="28" t="s">
+      <c r="J33" s="34" t="s">
         <v>977</v>
       </c>
-      <c r="J33" s="16" t="s">
+      <c r="K33" s="25" t="s">
         <v>978</v>
       </c>
-      <c r="K33" s="23" t="s">
+      <c r="L33" s="25" t="s">
         <v>979</v>
       </c>
-      <c r="L33" s="23" t="s">
+      <c r="M33" s="25" t="s">
         <v>980</v>
       </c>
-      <c r="M33" s="23" t="s">
+      <c r="N33" s="18">
+        <v>6072</v>
+      </c>
+      <c r="O33" s="18" t="s">
         <v>981</v>
       </c>
-      <c r="N33" s="16">
-        <v>6072</v>
-      </c>
-      <c r="O33" s="16" t="s">
+      <c r="P33" s="27" t="s">
         <v>982</v>
       </c>
-      <c r="P33" s="25" t="s">
+      <c r="Q33" s="27" t="s">
         <v>983</v>
       </c>
-      <c r="Q33" s="25" t="s">
+      <c r="R33" s="25" t="s">
         <v>984</v>
       </c>
-      <c r="R33" s="23" t="s">
+      <c r="S33" s="28" t="s">
         <v>985</v>
       </c>
-      <c r="S33" s="26" t="s">
+      <c r="T33" s="29" t="s">
         <v>986</v>
       </c>
-      <c r="T33" s="27" t="s">
+      <c r="U33" s="31" t="s">
         <v>987</v>
       </c>
-      <c r="U33" s="29" t="s">
+      <c r="V33" s="25" t="s">
         <v>988</v>
       </c>
-      <c r="V33" s="23" t="s">
+      <c r="W33" s="51" t="s">
         <v>989</v>
       </c>
-      <c r="W33" s="34" t="s">
+      <c r="X33" s="51" t="s">
         <v>990</v>
       </c>
-      <c r="X33" s="34" t="s">
+      <c r="Y33" s="56" t="s">
         <v>991</v>
       </c>
-      <c r="Y33" s="36" t="s">
+      <c r="Z33" s="51" t="s">
         <v>992</v>
       </c>
-      <c r="Z33" s="34" t="s">
+      <c r="AA33" s="53" t="s">
         <v>993</v>
       </c>
-      <c r="AA33" s="37" t="s">
+      <c r="AB33" s="30" t="s">
         <v>994</v>
       </c>
-      <c r="AB33" s="28" t="s">
+      <c r="AC33" s="51" t="s">
         <v>995</v>
       </c>
-      <c r="AC33" s="34" t="s">
+      <c r="AD33" s="25" t="s">
         <v>996</v>
       </c>
-      <c r="AD33" s="23" t="s">
+      <c r="AE33" s="25" t="s">
         <v>997</v>
-      </c>
-      <c r="AE33" s="23" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="47" t="s">
+        <v>998</v>
+      </c>
+      <c r="B34" s="25" t="s">
         <v>999</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="C34" s="18" t="s">
         <v>1000</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="D34" s="26" t="s">
         <v>1001</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="E34" s="25" t="s">
         <v>1002</v>
       </c>
-      <c r="E34" s="23" t="s">
+      <c r="F34" s="27" t="s">
         <v>1003</v>
       </c>
-      <c r="F34" s="25" t="s">
+      <c r="G34" s="28" t="s">
         <v>1004</v>
       </c>
-      <c r="G34" s="26" t="s">
+      <c r="H34" s="29" t="s">
         <v>1005</v>
       </c>
-      <c r="H34" s="27" t="s">
+      <c r="I34" s="30" t="s">
         <v>1006</v>
       </c>
-      <c r="I34" s="28" t="s">
+      <c r="J34" s="18" t="s">
         <v>1007</v>
       </c>
-      <c r="J34" s="16" t="s">
+      <c r="K34" s="25" t="s">
         <v>1008</v>
       </c>
-      <c r="K34" s="23" t="s">
+      <c r="L34" s="25" t="s">
         <v>1009</v>
       </c>
-      <c r="L34" s="23" t="s">
+      <c r="M34" s="25" t="s">
         <v>1010</v>
       </c>
-      <c r="M34" s="23" t="s">
+      <c r="N34" s="18">
+        <v>6676</v>
+      </c>
+      <c r="O34" s="18" t="s">
         <v>1011</v>
       </c>
-      <c r="N34" s="16">
-        <v>6676</v>
-      </c>
-      <c r="O34" s="16" t="s">
+      <c r="P34" s="27" t="s">
         <v>1012</v>
       </c>
-      <c r="P34" s="25" t="s">
+      <c r="Q34" s="27" t="s">
         <v>1013</v>
       </c>
-      <c r="Q34" s="25" t="s">
+      <c r="R34" s="25" t="s">
         <v>1014</v>
       </c>
-      <c r="R34" s="23" t="s">
+      <c r="S34" s="28" t="s">
         <v>1015</v>
       </c>
-      <c r="S34" s="26" t="s">
+      <c r="T34" s="29" t="s">
         <v>1016</v>
       </c>
-      <c r="T34" s="27" t="s">
+      <c r="U34" s="31" t="s">
         <v>1017</v>
       </c>
-      <c r="U34" s="29" t="s">
+      <c r="V34" s="25" t="s">
         <v>1018</v>
       </c>
-      <c r="V34" s="23" t="s">
+      <c r="W34" s="25" t="s">
         <v>1019</v>
       </c>
-      <c r="W34" s="23" t="s">
+      <c r="X34" s="18" t="s">
         <v>1020</v>
       </c>
-      <c r="X34" s="16" t="s">
+      <c r="Y34" s="18">
+        <v>6013</v>
+      </c>
+      <c r="Z34" s="25" t="s">
         <v>1021</v>
       </c>
-      <c r="Y34" s="16">
-        <v>6013</v>
-      </c>
-      <c r="Z34" s="23" t="s">
+      <c r="AA34" s="27" t="s">
         <v>1022</v>
       </c>
-      <c r="AA34" s="25" t="s">
+      <c r="AB34" s="31" t="s">
         <v>1023</v>
       </c>
-      <c r="AB34" s="29" t="s">
+      <c r="AC34" s="25" t="s">
         <v>1024</v>
       </c>
-      <c r="AC34" s="23" t="s">
+      <c r="AD34" s="25" t="s">
         <v>1025</v>
       </c>
-      <c r="AD34" s="23" t="s">
+      <c r="AE34" s="25" t="s">
         <v>1026</v>
-      </c>
-      <c r="AE34" s="23" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="47" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B35" s="25" t="s">
         <v>1028</v>
       </c>
-      <c r="B35" s="23" t="s">
+      <c r="C35" s="41" t="s">
         <v>1029</v>
       </c>
-      <c r="C35" s="16" t="s">
+      <c r="D35" s="26" t="s">
         <v>1030</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="E35" s="25" t="s">
         <v>1031</v>
       </c>
-      <c r="E35" s="23" t="s">
+      <c r="F35" s="27" t="s">
         <v>1032</v>
       </c>
-      <c r="F35" s="25" t="s">
+      <c r="G35" s="48" t="s">
         <v>1033</v>
       </c>
-      <c r="G35" s="31" t="s">
+      <c r="H35" s="49" t="s">
         <v>1034</v>
       </c>
-      <c r="H35" s="32" t="s">
+      <c r="I35" s="30" t="s">
         <v>1035</v>
       </c>
-      <c r="I35" s="28" t="s">
+      <c r="J35" s="18" t="s">
         <v>1036</v>
       </c>
-      <c r="J35" s="16" t="s">
+      <c r="K35" s="25" t="s">
         <v>1037</v>
       </c>
-      <c r="K35" s="23" t="s">
+      <c r="L35" s="25" t="s">
         <v>1038</v>
       </c>
-      <c r="L35" s="23" t="s">
+      <c r="M35" s="25" t="s">
         <v>1039</v>
       </c>
-      <c r="M35" s="23" t="s">
+      <c r="N35" s="18">
+        <v>6868</v>
+      </c>
+      <c r="O35" s="18" t="s">
         <v>1040</v>
       </c>
-      <c r="N35" s="16">
-        <v>6868</v>
-      </c>
-      <c r="O35" s="16" t="s">
+      <c r="P35" s="27" t="s">
         <v>1041</v>
       </c>
-      <c r="P35" s="25" t="s">
+      <c r="Q35" s="27" t="s">
         <v>1042</v>
       </c>
-      <c r="Q35" s="25" t="s">
+      <c r="R35" s="25" t="s">
         <v>1043</v>
       </c>
-      <c r="R35" s="23" t="s">
+      <c r="S35" s="28" t="s">
         <v>1044</v>
       </c>
-      <c r="S35" s="26" t="s">
+      <c r="T35" s="29" t="s">
         <v>1045</v>
       </c>
-      <c r="T35" s="27" t="s">
+      <c r="U35" s="31" t="s">
         <v>1046</v>
       </c>
-      <c r="U35" s="29" t="s">
+      <c r="V35" s="25" t="s">
         <v>1047</v>
       </c>
-      <c r="V35" s="23" t="s">
+      <c r="W35" s="25" t="s">
         <v>1048</v>
       </c>
-      <c r="W35" s="23" t="s">
+      <c r="X35" s="18" t="s">
         <v>1049</v>
       </c>
-      <c r="X35" s="16" t="s">
+      <c r="Y35" s="18">
+        <v>6617</v>
+      </c>
+      <c r="Z35" s="25" t="s">
         <v>1050</v>
       </c>
-      <c r="Y35" s="16">
-        <v>6617</v>
-      </c>
-      <c r="Z35" s="23" t="s">
+      <c r="AA35" s="27" t="s">
         <v>1051</v>
       </c>
-      <c r="AA35" s="25" t="s">
+      <c r="AB35" s="31" t="s">
         <v>1052</v>
       </c>
-      <c r="AB35" s="29" t="s">
+      <c r="AC35" s="25" t="s">
         <v>1053</v>
       </c>
-      <c r="AC35" s="23" t="s">
+      <c r="AD35" s="25" t="s">
         <v>1054</v>
       </c>
-      <c r="AD35" s="23" t="s">
+      <c r="AE35" s="25" t="s">
         <v>1055</v>
-      </c>
-      <c r="AE35" s="23" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="47" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B36" s="25" t="s">
         <v>1057</v>
       </c>
-      <c r="B36" s="23" t="s">
+      <c r="C36" s="18" t="s">
         <v>1058</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="D36" s="18" t="s">
         <v>1059</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="E36" s="25" t="s">
         <v>1060</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="F36" s="27" t="s">
         <v>1061</v>
       </c>
-      <c r="F36" s="25" t="s">
+      <c r="G36" s="48" t="s">
         <v>1062</v>
       </c>
-      <c r="G36" s="31" t="s">
+      <c r="H36" s="49" t="s">
         <v>1063</v>
       </c>
-      <c r="H36" s="32" t="s">
+      <c r="I36" s="30" t="s">
         <v>1064</v>
       </c>
-      <c r="I36" s="28" t="s">
+      <c r="J36" s="18" t="s">
         <v>1065</v>
       </c>
-      <c r="J36" s="16" t="s">
+      <c r="K36" s="40" t="s">
         <v>1066</v>
       </c>
-      <c r="K36" s="23" t="s">
+      <c r="L36" s="40" t="s">
         <v>1067</v>
       </c>
-      <c r="L36" s="23" t="s">
+      <c r="M36" s="40" t="s">
         <v>1068</v>
       </c>
-      <c r="M36" s="23" t="s">
+      <c r="N36" s="41">
+        <v>6092</v>
+      </c>
+      <c r="O36" s="41" t="s">
         <v>1069</v>
       </c>
-      <c r="N36" s="16">
-        <v>6064</v>
-      </c>
-      <c r="O36" s="16" t="s">
+      <c r="P36" s="43" t="s">
         <v>1070</v>
       </c>
-      <c r="P36" s="25" t="s">
+      <c r="Q36" s="43" t="s">
         <v>1071</v>
       </c>
-      <c r="Q36" s="25" t="s">
+      <c r="R36" s="40" t="s">
         <v>1072</v>
       </c>
-      <c r="R36" s="23" t="s">
+      <c r="S36" s="44" t="s">
         <v>1073</v>
       </c>
-      <c r="S36" s="26" t="s">
+      <c r="T36" s="45" t="s">
         <v>1074</v>
       </c>
-      <c r="T36" s="27" t="s">
+      <c r="U36" s="31" t="s">
         <v>1075</v>
       </c>
-      <c r="U36" s="29" t="s">
+      <c r="V36" s="25" t="s">
         <v>1076</v>
       </c>
-      <c r="V36" s="23" t="s">
+      <c r="W36" s="25" t="s">
         <v>1077</v>
       </c>
-      <c r="W36" s="23" t="s">
+      <c r="X36" s="18" t="s">
         <v>1078</v>
       </c>
-      <c r="X36" s="16" t="s">
+      <c r="Y36" s="18" t="s">
         <v>1079</v>
       </c>
-      <c r="Y36" s="16" t="s">
+      <c r="Z36" s="25" t="s">
         <v>1080</v>
       </c>
-      <c r="Z36" s="23" t="s">
+      <c r="AA36" s="27" t="s">
         <v>1081</v>
       </c>
-      <c r="AA36" s="25" t="s">
+      <c r="AB36" s="31" t="s">
         <v>1082</v>
       </c>
-      <c r="AB36" s="29" t="s">
+      <c r="AC36" s="25" t="s">
         <v>1083</v>
       </c>
-      <c r="AC36" s="23" t="s">
+      <c r="AD36" s="25" t="s">
         <v>1084</v>
       </c>
-      <c r="AD36" s="23" t="s">
+      <c r="AE36" s="25" t="s">
         <v>1085</v>
-      </c>
-      <c r="AE36" s="23" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25" ht="18" customHeight="1">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="47" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B37" s="25" t="s">
         <v>1087</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="C37" s="18" t="s">
         <v>1088</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="D37" s="18" t="s">
         <v>1089</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="E37" s="25" t="s">
         <v>1090</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="F37" s="27" t="s">
         <v>1091</v>
       </c>
-      <c r="F37" s="25" t="s">
+      <c r="G37" s="28" t="s">
         <v>1092</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="H37" s="29" t="s">
         <v>1093</v>
       </c>
-      <c r="H37" s="27" t="s">
+      <c r="I37" s="30" t="s">
         <v>1094</v>
       </c>
-      <c r="I37" s="28" t="s">
+      <c r="J37" s="18" t="s">
         <v>1095</v>
       </c>
-      <c r="J37" s="16" t="s">
+      <c r="K37" s="25" t="s">
         <v>1096</v>
       </c>
-      <c r="K37" s="23" t="s">
+      <c r="L37" s="25" t="s">
         <v>1097</v>
       </c>
-      <c r="L37" s="23" t="s">
+      <c r="M37" s="25" t="s">
         <v>1098</v>
       </c>
-      <c r="M37" s="23" t="s">
+      <c r="N37" s="18" t="s">
         <v>1099</v>
       </c>
-      <c r="N37" s="16" t="s">
+      <c r="O37" s="18" t="s">
         <v>1100</v>
       </c>
-      <c r="O37" s="16" t="s">
+      <c r="P37" s="27" t="s">
         <v>1101</v>
       </c>
-      <c r="P37" s="25" t="s">
+      <c r="Q37" s="27" t="s">
         <v>1102</v>
       </c>
-      <c r="Q37" s="25" t="s">
+      <c r="R37" s="25" t="s">
         <v>1103</v>
       </c>
-      <c r="R37" s="23" t="s">
+      <c r="S37" s="28" t="s">
         <v>1104</v>
       </c>
-      <c r="S37" s="26" t="s">
+      <c r="T37" s="29" t="s">
         <v>1105</v>
       </c>
-      <c r="T37" s="27" t="s">
+      <c r="U37" s="31" t="s">
         <v>1106</v>
       </c>
-      <c r="U37" s="29" t="s">
+      <c r="V37" s="25" t="s">
         <v>1107</v>
       </c>
-      <c r="V37" s="23" t="s">
+      <c r="W37" s="25" t="s">
         <v>1108</v>
       </c>
-      <c r="W37" s="23" t="s">
+      <c r="X37" s="18" t="s">
         <v>1109</v>
       </c>
-      <c r="X37" s="16" t="s">
+      <c r="Y37" s="18" t="s">
         <v>1110</v>
       </c>
-      <c r="Y37" s="16" t="s">
+      <c r="Z37" s="25" t="s">
         <v>1111</v>
       </c>
-      <c r="Z37" s="23" t="s">
+      <c r="AA37" s="27" t="s">
         <v>1112</v>
       </c>
-      <c r="AA37" s="25" t="s">
+      <c r="AB37" s="31" t="s">
         <v>1113</v>
       </c>
-      <c r="AB37" s="29" t="s">
+      <c r="AC37" s="25" t="s">
         <v>1114</v>
       </c>
-      <c r="AC37" s="23" t="s">
+      <c r="AD37" s="25" t="s">
         <v>1115</v>
       </c>
-      <c r="AD37" s="23" t="s">
+      <c r="AE37" s="25" t="s">
         <v>1116</v>
-      </c>
-      <c r="AE37" s="23" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="47" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B38" s="25" t="s">
         <v>1118</v>
       </c>
-      <c r="B38" s="23" t="s">
+      <c r="C38" s="18" t="s">
         <v>1119</v>
       </c>
-      <c r="C38" s="16" t="s">
+      <c r="D38" s="18" t="s">
         <v>1120</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="E38" s="25" t="s">
         <v>1121</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="F38" s="27" t="s">
         <v>1122</v>
       </c>
-      <c r="F38" s="25" t="s">
+      <c r="G38" s="28" t="s">
         <v>1123</v>
       </c>
-      <c r="G38" s="26" t="s">
+      <c r="H38" s="29" t="s">
         <v>1124</v>
       </c>
-      <c r="H38" s="27" t="s">
+      <c r="I38" s="30" t="s">
         <v>1125</v>
       </c>
-      <c r="I38" s="28" t="s">
+      <c r="J38" s="18" t="s">
         <v>1126</v>
       </c>
-      <c r="J38" s="16" t="s">
+      <c r="K38" s="25" t="s">
         <v>1127</v>
       </c>
-      <c r="K38" s="23" t="s">
+      <c r="L38" s="25" t="s">
         <v>1128</v>
       </c>
-      <c r="L38" s="23" t="s">
+      <c r="M38" s="25" t="s">
         <v>1129</v>
       </c>
-      <c r="M38" s="23" t="s">
+      <c r="N38" s="18" t="s">
         <v>1130</v>
       </c>
-      <c r="N38" s="16" t="s">
+      <c r="O38" s="18" t="s">
         <v>1131</v>
       </c>
-      <c r="O38" s="16" t="s">
+      <c r="P38" s="27" t="s">
         <v>1132</v>
       </c>
-      <c r="P38" s="25" t="s">
+      <c r="Q38" s="27" t="s">
         <v>1133</v>
       </c>
-      <c r="Q38" s="25" t="s">
+      <c r="R38" s="25" t="s">
         <v>1134</v>
       </c>
-      <c r="R38" s="23" t="s">
+      <c r="S38" s="28" t="s">
         <v>1135</v>
       </c>
-      <c r="S38" s="26" t="s">
+      <c r="T38" s="29" t="s">
         <v>1136</v>
       </c>
-      <c r="T38" s="27" t="s">
+      <c r="U38" s="31" t="s">
         <v>1137</v>
       </c>
-      <c r="U38" s="29" t="s">
+      <c r="V38" s="25" t="s">
         <v>1138</v>
       </c>
-      <c r="V38" s="23" t="s">
+      <c r="W38" s="25" t="s">
         <v>1139</v>
       </c>
-      <c r="W38" s="23" t="s">
+      <c r="X38" s="18" t="s">
         <v>1140</v>
       </c>
-      <c r="X38" s="16" t="s">
+      <c r="Y38" s="18" t="s">
         <v>1141</v>
       </c>
-      <c r="Y38" s="16" t="s">
+      <c r="Z38" s="25" t="s">
         <v>1142</v>
       </c>
-      <c r="Z38" s="23" t="s">
+      <c r="AA38" s="27" t="s">
         <v>1143</v>
       </c>
-      <c r="AA38" s="25" t="s">
+      <c r="AB38" s="31" t="s">
         <v>1144</v>
       </c>
-      <c r="AB38" s="29" t="s">
+      <c r="AC38" s="25" t="s">
         <v>1145</v>
       </c>
-      <c r="AC38" s="23" t="s">
+      <c r="AD38" s="25" t="s">
         <v>1146</v>
       </c>
-      <c r="AD38" s="23" t="s">
+      <c r="AE38" s="25" t="s">
         <v>1147</v>
-      </c>
-      <c r="AE38" s="23" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="47" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B39" s="25" t="s">
         <v>1149</v>
       </c>
-      <c r="B39" s="23" t="s">
+      <c r="C39" s="18" t="s">
         <v>1150</v>
       </c>
-      <c r="C39" s="16" t="s">
+      <c r="D39" s="56" t="s">
         <v>1151</v>
       </c>
-      <c r="D39" s="36" t="s">
+      <c r="E39" s="25" t="s">
         <v>1152</v>
       </c>
-      <c r="E39" s="23" t="s">
+      <c r="F39" s="27" t="s">
         <v>1153</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="G39" s="48" t="s">
         <v>1154</v>
       </c>
-      <c r="G39" s="31" t="s">
+      <c r="H39" s="49" t="s">
         <v>1155</v>
       </c>
-      <c r="H39" s="32" t="s">
+      <c r="I39" s="30" t="s">
         <v>1156</v>
       </c>
-      <c r="I39" s="28" t="s">
+      <c r="J39" s="18" t="s">
         <v>1157</v>
       </c>
-      <c r="J39" s="16" t="s">
+      <c r="K39" s="25" t="s">
         <v>1158</v>
       </c>
-      <c r="K39" s="23" t="s">
+      <c r="L39" s="25" t="s">
         <v>1159</v>
       </c>
-      <c r="L39" s="23" t="s">
+      <c r="M39" s="25" t="s">
         <v>1160</v>
       </c>
-      <c r="M39" s="23" t="s">
+      <c r="N39" s="56" t="s">
         <v>1161</v>
       </c>
-      <c r="N39" s="36" t="s">
+      <c r="O39" s="18" t="s">
         <v>1162</v>
       </c>
-      <c r="O39" s="16" t="s">
+      <c r="P39" s="27" t="s">
         <v>1163</v>
       </c>
-      <c r="P39" s="25" t="s">
+      <c r="Q39" s="27" t="s">
         <v>1164</v>
       </c>
-      <c r="Q39" s="25" t="s">
+      <c r="R39" s="25" t="s">
         <v>1165</v>
       </c>
-      <c r="R39" s="23" t="s">
+      <c r="S39" s="28" t="s">
         <v>1166</v>
       </c>
-      <c r="S39" s="26" t="s">
+      <c r="T39" s="29" t="s">
         <v>1167</v>
       </c>
-      <c r="T39" s="27" t="s">
+      <c r="U39" s="31" t="s">
         <v>1168</v>
       </c>
-      <c r="U39" s="29" t="s">
+      <c r="V39" s="25" t="s">
         <v>1169</v>
       </c>
-      <c r="V39" s="23" t="s">
+      <c r="W39" s="25" t="s">
         <v>1170</v>
       </c>
-      <c r="W39" s="23" t="s">
+      <c r="X39" s="18" t="s">
         <v>1171</v>
       </c>
-      <c r="X39" s="16" t="s">
+      <c r="Y39" s="56" t="s">
         <v>1172</v>
       </c>
-      <c r="Y39" s="36" t="s">
+      <c r="Z39" s="25" t="s">
         <v>1173</v>
       </c>
-      <c r="Z39" s="23" t="s">
+      <c r="AA39" s="27" t="s">
         <v>1174</v>
       </c>
-      <c r="AA39" s="25" t="s">
+      <c r="AB39" s="31" t="s">
         <v>1175</v>
       </c>
-      <c r="AB39" s="29" t="s">
+      <c r="AC39" s="25" t="s">
         <v>1176</v>
       </c>
-      <c r="AC39" s="23" t="s">
+      <c r="AD39" s="25" t="s">
         <v>1177</v>
       </c>
-      <c r="AD39" s="23" t="s">
+      <c r="AE39" s="25" t="s">
         <v>1178</v>
-      </c>
-      <c r="AE39" s="23" t="s">
-        <v>1179</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25" ht="19" customHeight="1">
-      <c r="A40" s="42" t="s">
+      <c r="A40" s="70" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B40" s="71" t="s">
         <v>1180</v>
       </c>
-      <c r="B40" s="43" t="s">
+      <c r="C40" s="72" t="s">
         <v>1181</v>
       </c>
-      <c r="C40" s="44" t="s">
+      <c r="D40" s="73" t="s">
         <v>1182</v>
       </c>
-      <c r="D40" s="45" t="s">
+      <c r="E40" s="71" t="s">
         <v>1183</v>
       </c>
-      <c r="E40" s="43" t="s">
+      <c r="F40" s="74" t="s">
         <v>1184</v>
       </c>
-      <c r="F40" s="46" t="s">
+      <c r="G40" s="75" t="s">
         <v>1185</v>
       </c>
-      <c r="G40" s="47" t="s">
+      <c r="H40" s="76" t="s">
         <v>1186</v>
       </c>
-      <c r="H40" s="48" t="s">
+      <c r="I40" s="77" t="s">
         <v>1187</v>
       </c>
-      <c r="I40" s="49" t="s">
+      <c r="J40" s="72" t="s">
         <v>1188</v>
       </c>
-      <c r="J40" s="44" t="s">
+      <c r="K40" s="71" t="s">
         <v>1189</v>
       </c>
-      <c r="K40" s="43" t="s">
+      <c r="L40" s="71" t="s">
         <v>1190</v>
       </c>
-      <c r="L40" s="43" t="s">
+      <c r="M40" s="71" t="s">
         <v>1191</v>
       </c>
-      <c r="M40" s="43" t="s">
+      <c r="N40" s="73" t="s">
         <v>1192</v>
       </c>
-      <c r="N40" s="45" t="s">
+      <c r="O40" s="72" t="s">
         <v>1193</v>
       </c>
-      <c r="O40" s="44" t="s">
+      <c r="P40" s="74" t="s">
         <v>1194</v>
       </c>
-      <c r="P40" s="46" t="s">
+      <c r="Q40" s="74" t="s">
         <v>1195</v>
       </c>
-      <c r="Q40" s="46" t="s">
+      <c r="R40" s="71" t="s">
         <v>1196</v>
       </c>
-      <c r="R40" s="43" t="s">
+      <c r="S40" s="78" t="s">
         <v>1197</v>
       </c>
-      <c r="S40" s="50" t="s">
+      <c r="T40" s="79" t="s">
         <v>1198</v>
       </c>
-      <c r="T40" s="51" t="s">
+      <c r="U40" s="80" t="s">
         <v>1199</v>
       </c>
-      <c r="U40" s="52" t="s">
+      <c r="V40" s="71" t="s">
         <v>1200</v>
       </c>
-      <c r="V40" s="43" t="s">
+      <c r="W40" s="71" t="s">
         <v>1201</v>
       </c>
-      <c r="W40" s="43" t="s">
+      <c r="X40" s="72" t="s">
         <v>1202</v>
       </c>
-      <c r="X40" s="44" t="s">
+      <c r="Y40" s="73" t="s">
         <v>1203</v>
       </c>
-      <c r="Y40" s="45" t="s">
+      <c r="Z40" s="71" t="s">
         <v>1204</v>
       </c>
-      <c r="Z40" s="43" t="s">
+      <c r="AA40" s="74" t="s">
         <v>1205</v>
       </c>
-      <c r="AA40" s="46" t="s">
+      <c r="AB40" s="80" t="s">
         <v>1206</v>
       </c>
-      <c r="AB40" s="52" t="s">
+      <c r="AC40" s="71" t="s">
         <v>1207</v>
       </c>
-      <c r="AC40" s="43" t="s">
+      <c r="AD40" s="71" t="s">
         <v>1208</v>
       </c>
-      <c r="AD40" s="43" t="s">
+      <c r="AE40" s="71" t="s">
         <v>1209</v>
-      </c>
-      <c r="AE40" s="43" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25" ht="21" customHeight="1">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="81" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B41" s="0" t="s">
         <v>1211</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="C41" s="0" t="s">
         <v>1212</v>
       </c>
-      <c r="C41" s="0" t="s">
+      <c r="D41" s="0" t="s">
         <v>1213</v>
       </c>
-      <c r="D41" s="0" t="s">
+      <c r="E41" s="0" t="s">
         <v>1214</v>
       </c>
-      <c r="E41" s="0" t="s">
+      <c r="F41" s="0" t="s">
         <v>1215</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="G41" s="0" t="s">
         <v>1216</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="H41" s="0" t="s">
         <v>1217</v>
       </c>
-      <c r="H41" s="0" t="s">
+      <c r="I41" s="0" t="s">
         <v>1218</v>
       </c>
-      <c r="I41" s="0" t="s">
+      <c r="J41" s="0" t="s">
         <v>1219</v>
       </c>
-      <c r="J41" s="0" t="s">
+      <c r="K41" s="0" t="s">
         <v>1220</v>
       </c>
-      <c r="K41" s="0" t="s">
+      <c r="L41" s="0" t="s">
         <v>1221</v>
       </c>
-      <c r="L41" s="0" t="s">
+      <c r="M41" s="0" t="s">
         <v>1222</v>
       </c>
-      <c r="M41" s="0" t="s">
+      <c r="N41" s="0" t="s">
         <v>1223</v>
       </c>
-      <c r="N41" s="0" t="s">
+      <c r="O41" s="0" t="s">
         <v>1224</v>
       </c>
-      <c r="O41" s="0" t="s">
+      <c r="P41" s="0" t="s">
         <v>1225</v>
       </c>
-      <c r="P41" s="0" t="s">
+      <c r="Q41" s="0" t="s">
         <v>1226</v>
       </c>
-      <c r="Q41" s="0" t="s">
+      <c r="R41" s="0" t="s">
         <v>1227</v>
       </c>
-      <c r="R41" s="0" t="s">
+      <c r="S41" s="0" t="s">
         <v>1228</v>
       </c>
-      <c r="S41" s="0" t="s">
+      <c r="T41" s="0" t="s">
         <v>1229</v>
       </c>
-      <c r="T41" s="0" t="s">
+      <c r="U41" s="0" t="s">
         <v>1230</v>
       </c>
-      <c r="U41" s="0" t="s">
+      <c r="V41" s="0" t="s">
         <v>1231</v>
       </c>
-      <c r="V41" s="0" t="s">
+      <c r="W41" s="0" t="s">
         <v>1232</v>
       </c>
-      <c r="W41" s="0" t="s">
+      <c r="X41" s="0" t="s">
         <v>1233</v>
       </c>
-      <c r="X41" s="0" t="s">
+      <c r="Y41" s="0" t="s">
         <v>1234</v>
       </c>
-      <c r="Y41" s="0" t="s">
+      <c r="Z41" s="0" t="s">
         <v>1235</v>
       </c>
-      <c r="Z41" s="0" t="s">
+      <c r="AA41" s="0" t="s">
         <v>1236</v>
       </c>
-      <c r="AA41" s="0" t="s">
+      <c r="AB41" s="0" t="s">
         <v>1237</v>
       </c>
-      <c r="AB41" s="0" t="s">
+      <c r="AC41" s="0" t="s">
         <v>1238</v>
       </c>
-      <c r="AC41" s="0" t="s">
+      <c r="AD41" s="0" t="s">
         <v>1239</v>
       </c>
-      <c r="AD41" s="0" t="s">
+      <c r="AE41" s="0" t="s">
         <v>1240</v>
-      </c>
-      <c r="AE41" s="0" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25" ht="23" customHeight="1">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="82" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B42" s="0" t="s">
         <v>1242</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="C42" s="0" t="s">
         <v>1243</v>
       </c>
-      <c r="C42" s="0" t="s">
+      <c r="D42" s="0" t="s">
         <v>1244</v>
       </c>
-      <c r="D42" s="0" t="s">
+      <c r="E42" s="0" t="s">
         <v>1245</v>
       </c>
-      <c r="E42" s="0" t="s">
+      <c r="F42" s="0" t="s">
         <v>1246</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="G42" s="0" t="s">
         <v>1247</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="H42" s="0" t="s">
         <v>1248</v>
       </c>
-      <c r="H42" s="0" t="s">
+      <c r="I42" s="0" t="s">
         <v>1249</v>
       </c>
-      <c r="I42" s="0" t="s">
+      <c r="J42" s="0" t="s">
         <v>1250</v>
       </c>
-      <c r="J42" s="0" t="s">
+      <c r="K42" s="0" t="s">
         <v>1251</v>
       </c>
-      <c r="K42" s="0" t="s">
+      <c r="L42" s="0" t="s">
         <v>1252</v>
       </c>
-      <c r="L42" s="0" t="s">
+      <c r="M42" s="0" t="s">
         <v>1253</v>
       </c>
-      <c r="M42" s="0" t="s">
+      <c r="N42" s="0" t="s">
         <v>1254</v>
       </c>
-      <c r="N42" s="0" t="s">
+      <c r="O42" s="0" t="s">
         <v>1255</v>
       </c>
-      <c r="O42" s="0" t="s">
+      <c r="P42" s="0" t="s">
         <v>1256</v>
       </c>
-      <c r="P42" s="0" t="s">
+      <c r="Q42" s="0" t="s">
         <v>1257</v>
       </c>
-      <c r="Q42" s="0" t="s">
+      <c r="R42" s="0" t="s">
         <v>1258</v>
       </c>
-      <c r="R42" s="0" t="s">
+      <c r="S42" s="0" t="s">
         <v>1259</v>
       </c>
-      <c r="S42" s="0" t="s">
+      <c r="T42" s="0" t="s">
         <v>1260</v>
       </c>
-      <c r="T42" s="0" t="s">
+      <c r="U42" s="0" t="s">
         <v>1261</v>
       </c>
-      <c r="U42" s="0" t="s">
+      <c r="V42" s="0" t="s">
         <v>1262</v>
       </c>
-      <c r="V42" s="0" t="s">
+      <c r="W42" s="0" t="s">
         <v>1263</v>
       </c>
-      <c r="W42" s="0" t="s">
+      <c r="X42" s="0" t="s">
         <v>1264</v>
       </c>
-      <c r="X42" s="0" t="s">
+      <c r="Y42" s="0" t="s">
         <v>1265</v>
       </c>
-      <c r="Y42" s="0" t="s">
+      <c r="Z42" s="0" t="s">
         <v>1266</v>
       </c>
-      <c r="Z42" s="0" t="s">
+      <c r="AA42" s="0" t="s">
         <v>1267</v>
       </c>
-      <c r="AA42" s="0" t="s">
+      <c r="AB42" s="0" t="s">
         <v>1268</v>
       </c>
-      <c r="AB42" s="0" t="s">
+      <c r="AC42" s="0" t="s">
         <v>1269</v>
       </c>
-      <c r="AC42" s="0" t="s">
+      <c r="AD42" s="0" t="s">
         <v>1270</v>
       </c>
-      <c r="AD42" s="0" t="s">
+      <c r="AE42" s="0" t="s">
         <v>1271</v>
-      </c>
-      <c r="AE42" s="0" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25" ht="13" customHeight="1">
-      <c r="A43" s="55" t="s">
+      <c r="A43" s="83" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B43" s="84" t="s">
         <v>1273</v>
       </c>
-      <c r="B43" s="56" t="s">
+      <c r="C43" s="84" t="s">
         <v>1274</v>
       </c>
-      <c r="C43" s="56" t="s">
+      <c r="D43" s="84" t="s">
         <v>1275</v>
       </c>
-      <c r="D43" s="56" t="s">
+      <c r="E43" s="84" t="s">
         <v>1276</v>
       </c>
-      <c r="E43" s="56" t="s">
+      <c r="F43" s="84" t="s">
         <v>1277</v>
       </c>
-      <c r="F43" s="56" t="s">
+      <c r="G43" s="84" t="s">
         <v>1278</v>
       </c>
-      <c r="G43" s="56" t="s">
+      <c r="H43" s="84" t="s">
         <v>1279</v>
       </c>
-      <c r="H43" s="56" t="s">
+      <c r="I43" s="84" t="s">
         <v>1280</v>
       </c>
-      <c r="I43" s="56" t="s">
+      <c r="J43" s="84" t="s">
         <v>1281</v>
       </c>
-      <c r="J43" s="56" t="s">
+      <c r="K43" s="84" t="s">
         <v>1282</v>
       </c>
-      <c r="K43" s="56" t="s">
+      <c r="L43" s="84" t="s">
         <v>1283</v>
       </c>
-      <c r="L43" s="56" t="s">
+      <c r="M43" s="84" t="s">
         <v>1284</v>
       </c>
-      <c r="M43" s="56" t="s">
+      <c r="N43" s="84" t="s">
         <v>1285</v>
       </c>
-      <c r="N43" s="56" t="s">
+      <c r="O43" s="84" t="s">
         <v>1286</v>
       </c>
-      <c r="O43" s="56" t="s">
+      <c r="P43" s="84" t="s">
         <v>1287</v>
       </c>
-      <c r="P43" s="56" t="s">
+      <c r="Q43" s="84" t="s">
         <v>1288</v>
       </c>
-      <c r="Q43" s="56" t="s">
+      <c r="R43" s="84" t="s">
         <v>1289</v>
       </c>
-      <c r="R43" s="56" t="s">
+      <c r="S43" s="84" t="s">
         <v>1290</v>
       </c>
-      <c r="S43" s="56" t="s">
+      <c r="T43" s="84" t="s">
         <v>1291</v>
       </c>
-      <c r="T43" s="56" t="s">
+      <c r="U43" s="84" t="s">
         <v>1292</v>
       </c>
-      <c r="U43" s="56" t="s">
+      <c r="V43" s="84" t="s">
         <v>1293</v>
       </c>
-      <c r="V43" s="56" t="s">
+      <c r="W43" s="84" t="s">
         <v>1294</v>
       </c>
-      <c r="W43" s="56" t="s">
+      <c r="X43" s="84" t="s">
         <v>1295</v>
       </c>
-      <c r="X43" s="56" t="s">
+      <c r="Y43" s="84" t="s">
         <v>1296</v>
       </c>
-      <c r="Y43" s="56" t="s">
+      <c r="Z43" s="84" t="s">
         <v>1297</v>
       </c>
-      <c r="Z43" s="56" t="s">
+      <c r="AA43" s="84" t="s">
         <v>1298</v>
       </c>
-      <c r="AA43" s="56" t="s">
+      <c r="AB43" s="84" t="s">
         <v>1299</v>
       </c>
-      <c r="AB43" s="56" t="s">
+      <c r="AC43" s="84" t="s">
         <v>1300</v>
       </c>
-      <c r="AC43" s="56" t="s">
+      <c r="AD43" s="84" t="s">
         <v>1301</v>
       </c>
-      <c r="AD43" s="56" t="s">
+      <c r="AE43" s="84" t="s">
         <v>1302</v>
-      </c>
-      <c r="AE43" s="56" t="s">
-        <v>1303</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25" ht="10" customHeight="1">
-      <c r="A44" s="57" t="s">
+      <c r="A44" s="85" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B44" s="86" t="s">
         <v>1304</v>
       </c>
-      <c r="B44" s="58" t="s">
+      <c r="C44" s="87" t="s">
         <v>1305</v>
       </c>
-      <c r="C44" s="59" t="s">
+      <c r="D44" s="88" t="s">
         <v>1306</v>
       </c>
-      <c r="D44" s="60" t="s">
+      <c r="E44" s="89" t="s">
         <v>1307</v>
       </c>
-      <c r="E44" s="61" t="s">
+      <c r="F44" s="90" t="s">
         <v>1308</v>
       </c>
-      <c r="F44" s="62" t="s">
+      <c r="G44" s="89" t="s">
         <v>1309</v>
       </c>
-      <c r="G44" s="61" t="s">
+      <c r="H44" s="90" t="s">
         <v>1310</v>
       </c>
-      <c r="H44" s="62" t="s">
+      <c r="I44" s="91" t="s">
         <v>1311</v>
       </c>
-      <c r="I44" s="63" t="s">
+      <c r="J44" s="90" t="s">
         <v>1312</v>
       </c>
-      <c r="J44" s="62" t="s">
+      <c r="K44" s="91" t="s">
         <v>1313</v>
       </c>
-      <c r="K44" s="63" t="s">
+      <c r="L44" s="90" t="s">
         <v>1314</v>
       </c>
-      <c r="L44" s="62" t="s">
+      <c r="M44" s="91" t="s">
         <v>1315</v>
       </c>
-      <c r="M44" s="63" t="s">
+      <c r="N44" s="87" t="s">
         <v>1316</v>
       </c>
-      <c r="N44" s="59" t="s">
+      <c r="O44" s="92" t="s">
         <v>1317</v>
       </c>
-      <c r="O44" s="64" t="s">
+      <c r="P44" s="93" t="s">
         <v>1318</v>
       </c>
-      <c r="P44" s="6" t="s">
+      <c r="Q44" s="93" t="s">
         <v>1319</v>
       </c>
-      <c r="Q44" s="6" t="s">
+      <c r="R44" s="93" t="s">
         <v>1320</v>
       </c>
-      <c r="R44" s="6" t="s">
+      <c r="S44" s="93" t="s">
         <v>1321</v>
       </c>
-      <c r="S44" s="6" t="s">
+      <c r="T44" s="94" t="s">
         <v>1322</v>
       </c>
-      <c r="T44" s="65" t="s">
+      <c r="U44" s="95" t="s">
         <v>1323</v>
       </c>
-      <c r="U44" s="66" t="s">
+      <c r="V44" s="96" t="s">
         <v>1324</v>
       </c>
-      <c r="V44" s="67" t="s">
+      <c r="W44" s="97" t="s">
         <v>1325</v>
       </c>
-      <c r="W44" s="68" t="s">
+      <c r="X44" s="96" t="s">
         <v>1326</v>
       </c>
-      <c r="X44" s="67" t="s">
+      <c r="Y44" s="98" t="s">
         <v>1327</v>
       </c>
-      <c r="Y44" s="69" t="s">
+      <c r="Z44" s="97" t="s">
         <v>1328</v>
       </c>
-      <c r="Z44" s="68" t="s">
+      <c r="AA44" s="93" t="s">
         <v>1329</v>
       </c>
-      <c r="AA44" s="6" t="s">
+      <c r="AB44" s="93" t="s">
         <v>1330</v>
       </c>
-      <c r="AB44" s="6" t="s">
+      <c r="AC44" s="93" t="s">
         <v>1331</v>
       </c>
-      <c r="AC44" s="6" t="s">
+      <c r="AD44" s="93" t="s">
         <v>1332</v>
-      </c>
-      <c r="AD44" s="6" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25" ht="13" customHeight="1">
-      <c r="A45" s="65" t="s">
+      <c r="A45" s="94" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B45" s="99" t="s">
         <v>1334</v>
       </c>
-      <c r="B45" s="70" t="s">
+      <c r="C45" s="87" t="s">
         <v>1335</v>
       </c>
-      <c r="C45" s="59" t="s">
+      <c r="D45" s="88" t="s">
         <v>1336</v>
       </c>
-      <c r="D45" s="60" t="s">
+      <c r="E45" s="100" t="s">
         <v>1337</v>
       </c>
-      <c r="E45" s="71" t="s">
+      <c r="F45" s="90" t="s">
         <v>1338</v>
       </c>
-      <c r="F45" s="62" t="s">
+      <c r="G45" s="100" t="s">
         <v>1339</v>
       </c>
-      <c r="G45" s="71" t="s">
+      <c r="H45" s="90" t="s">
         <v>1340</v>
       </c>
-      <c r="H45" s="62" t="s">
+      <c r="I45" s="101" t="s">
         <v>1341</v>
       </c>
-      <c r="I45" s="72" t="s">
+      <c r="J45" s="90" t="s">
         <v>1342</v>
       </c>
-      <c r="J45" s="62" t="s">
+      <c r="K45" s="101" t="s">
         <v>1343</v>
       </c>
-      <c r="K45" s="72" t="s">
+      <c r="L45" s="102" t="s">
         <v>1344</v>
       </c>
-      <c r="L45" s="73" t="s">
+      <c r="M45" s="15" t="s">
         <v>1345</v>
       </c>
-      <c r="M45" s="13" t="s">
+      <c r="N45" s="97" t="s">
         <v>1346</v>
       </c>
-      <c r="N45" s="68" t="s">
+      <c r="O45" s="93" t="s">
         <v>1347</v>
       </c>
-      <c r="O45" s="6" t="s">
+      <c r="P45" s="93" t="s">
         <v>1348</v>
       </c>
-      <c r="P45" s="6" t="s">
+      <c r="Q45" s="93" t="s">
         <v>1349</v>
       </c>
-      <c r="Q45" s="6" t="s">
+      <c r="R45" s="93" t="s">
         <v>1350</v>
       </c>
-      <c r="R45" s="6" t="s">
+      <c r="S45" s="93" t="s">
         <v>1351</v>
       </c>
-      <c r="S45" s="6" t="s">
+      <c r="T45" s="94" t="s">
         <v>1352</v>
       </c>
-      <c r="T45" s="65" t="s">
+      <c r="U45" s="10" t="s">
         <v>1353</v>
       </c>
-      <c r="U45" s="8" t="s">
+      <c r="V45" s="13" t="s">
         <v>1354</v>
       </c>
-      <c r="V45" s="11" t="s">
+      <c r="W45" s="97" t="s">
         <v>1355</v>
       </c>
-      <c r="W45" s="68" t="s">
+      <c r="X45" s="13" t="s">
         <v>1356</v>
       </c>
-      <c r="X45" s="11" t="s">
+      <c r="Y45" s="98" t="s">
         <v>1357</v>
       </c>
-      <c r="Y45" s="69" t="s">
+      <c r="Z45" s="97" t="s">
         <v>1358</v>
       </c>
-      <c r="Z45" s="68" t="s">
+      <c r="AA45" s="93" t="s">
         <v>1359</v>
       </c>
-      <c r="AA45" s="6" t="s">
+      <c r="AB45" s="93" t="s">
         <v>1360</v>
       </c>
-      <c r="AB45" s="6" t="s">
+      <c r="AC45" s="93" t="s">
         <v>1361</v>
       </c>
-      <c r="AC45" s="6" t="s">
+      <c r="AD45" s="93" t="s">
         <v>1362</v>
-      </c>
-      <c r="AD45" s="6" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25" ht="12" customHeight="1">
-      <c r="A46" s="57" t="s">
+      <c r="A46" s="85" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B46" s="100" t="s">
         <v>1364</v>
       </c>
-      <c r="B46" s="71" t="s">
+      <c r="C46" s="87" t="s">
         <v>1365</v>
       </c>
-      <c r="C46" s="59" t="s">
+      <c r="D46" s="103" t="s">
         <v>1366</v>
       </c>
-      <c r="D46" s="74" t="s">
+      <c r="E46" s="100" t="s">
         <v>1367</v>
       </c>
-      <c r="E46" s="71" t="s">
+      <c r="F46" s="90" t="s">
         <v>1368</v>
       </c>
-      <c r="F46" s="62" t="s">
+      <c r="G46" s="100" t="s">
         <v>1369</v>
       </c>
-      <c r="G46" s="71" t="s">
+      <c r="H46" s="87" t="s">
         <v>1370</v>
       </c>
-      <c r="H46" s="59" t="s">
+      <c r="I46" s="104" t="s">
         <v>1371</v>
       </c>
-      <c r="I46" s="75" t="s">
+      <c r="J46" s="105" t="s">
         <v>1372</v>
       </c>
-      <c r="J46" s="76" t="s">
+      <c r="K46" s="104" t="s">
         <v>1373</v>
       </c>
-      <c r="K46" s="75" t="s">
+      <c r="L46" s="105" t="s">
         <v>1374</v>
       </c>
-      <c r="L46" s="76" t="s">
+      <c r="M46" s="105" t="s">
         <v>1375</v>
       </c>
-      <c r="M46" s="76" t="s">
+      <c r="N46" s="105" t="s">
         <v>1376</v>
       </c>
-      <c r="N46" s="76" t="s">
+      <c r="O46" s="105" t="s">
         <v>1377</v>
       </c>
-      <c r="O46" s="76" t="s">
+      <c r="P46" s="105" t="s">
         <v>1378</v>
       </c>
-      <c r="P46" s="76" t="s">
+      <c r="Q46" s="105" t="s">
         <v>1379</v>
       </c>
-      <c r="Q46" s="76" t="s">
+      <c r="R46" s="105" t="s">
         <v>1380</v>
       </c>
-      <c r="R46" s="76" t="s">
+      <c r="S46" s="105" t="s">
         <v>1381</v>
       </c>
-      <c r="S46" s="76" t="s">
+      <c r="T46" s="105" t="s">
         <v>1382</v>
       </c>
-      <c r="T46" s="76" t="s">
+      <c r="U46" s="104" t="s">
         <v>1383</v>
       </c>
-      <c r="U46" s="75" t="s">
+      <c r="V46" s="104" t="s">
         <v>1384</v>
       </c>
-      <c r="V46" s="75" t="s">
+      <c r="W46" s="105" t="s">
         <v>1385</v>
       </c>
-      <c r="W46" s="76" t="s">
+      <c r="X46" s="104" t="s">
         <v>1386</v>
       </c>
-      <c r="X46" s="75" t="s">
+      <c r="Y46" s="105" t="s">
         <v>1387</v>
       </c>
-      <c r="Y46" s="76" t="s">
+      <c r="Z46" s="105" t="s">
         <v>1388</v>
       </c>
-      <c r="Z46" s="76" t="s">
+      <c r="AA46" s="105" t="s">
         <v>1389</v>
       </c>
-      <c r="AA46" s="76" t="s">
+      <c r="AB46" s="105" t="s">
         <v>1390</v>
       </c>
-      <c r="AB46" s="76" t="s">
+      <c r="AC46" s="105" t="s">
         <v>1391</v>
       </c>
-      <c r="AC46" s="76" t="s">
+      <c r="AD46" s="105" t="s">
         <v>1392</v>
-      </c>
-      <c r="AD46" s="76" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25" ht="10" customHeight="1">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="93" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B47" s="93" t="s">
         <v>1394</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="C47" s="93" t="s">
         <v>1395</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="D47" s="106" t="s">
         <v>1396</v>
       </c>
-      <c r="D47" s="77" t="s">
+      <c r="E47" s="107" t="s">
         <v>1397</v>
       </c>
-      <c r="E47" s="78" t="s">
+      <c r="F47" s="106" t="s">
         <v>1398</v>
       </c>
-      <c r="F47" s="77" t="s">
+      <c r="G47" s="107" t="s">
         <v>1399</v>
       </c>
-      <c r="G47" s="78" t="s">
+      <c r="H47" s="107" t="s">
         <v>1400</v>
       </c>
-      <c r="H47" s="78" t="s">
+      <c r="I47" s="108" t="s">
         <v>1401</v>
-      </c>
-      <c r="I47" s="79" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25" ht="6" customHeight="1">
-      <c r="A48" s="80" t="s">
+      <c r="A48" s="109" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B48" s="109" t="s">
         <v>1403</v>
       </c>
-      <c r="B48" s="80" t="s">
+      <c r="C48" s="109" t="s">
         <v>1404</v>
       </c>
-      <c r="C48" s="80" t="s">
+      <c r="D48" s="110" t="s">
         <v>1405</v>
       </c>
-      <c r="D48" s="81" t="s">
+      <c r="E48" s="110" t="s">
         <v>1406</v>
       </c>
-      <c r="E48" s="81" t="s">
+      <c r="F48" s="110" t="s">
         <v>1407</v>
       </c>
-      <c r="F48" s="81" t="s">
+      <c r="G48" s="111" t="s">
         <v>1408</v>
       </c>
-      <c r="G48" s="82" t="s">
+      <c r="H48" s="111" t="s">
         <v>1409</v>
       </c>
-      <c r="H48" s="82" t="s">
+      <c r="I48" s="109" t="s">
         <v>1410</v>
-      </c>
-      <c r="I48" s="80" t="s">
-        <v>1411</v>
       </c>
     </row>
   </sheetData>
